--- a/research/traditional_assets/database/data/austria/austria_transportation.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_transportation.xlsx
@@ -1203,7 +1203,7 @@
         <v>1.09730294675145</v>
       </c>
       <c r="Z2">
-        <v>0.929806307484137</v>
+        <v>0.929806307484138</v>
       </c>
       <c r="AA2">
         <v>896.9</v>
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08567392956617489</v>
+        <v>0.08550251213521608</v>
       </c>
       <c r="C2">
-        <v>2706.424855917861</v>
+        <v>2685.471239348594</v>
       </c>
       <c r="D2">
-        <v>2635.124855917861</v>
+        <v>2643.282239348594</v>
       </c>
       <c r="E2">
-        <v>-896.9</v>
+        <v>-867.789</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>29.111</v>
       </c>
       <c r="G2">
         <v>71.3</v>
@@ -1457,28 +1457,28 @@
         <v>112.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.4642833</v>
       </c>
       <c r="N2">
-        <v>112.5</v>
+        <v>111.0357167</v>
       </c>
       <c r="O2">
-        <v>26.99999999999999</v>
+        <v>26.64857200799999</v>
       </c>
       <c r="P2">
-        <v>85.49999999999997</v>
+        <v>84.38714469199998</v>
       </c>
       <c r="Q2">
-        <v>307.4</v>
+        <v>306.287144692</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08567392956617489</v>
+        <v>0.08598003245981423</v>
       </c>
       <c r="T2">
-        <v>0.8198499599185859</v>
+        <v>0.8261437575906883</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>76.82939496749022</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08550251213521608</v>
+        <v>0.08533109470425725</v>
       </c>
       <c r="C3">
-        <v>2685.471239348594</v>
+        <v>2664.568284163705</v>
       </c>
       <c r="D3">
-        <v>2643.282239348594</v>
+        <v>2651.490284163705</v>
       </c>
       <c r="E3">
-        <v>-867.789</v>
+        <v>-838.678</v>
       </c>
       <c r="F3">
-        <v>29.111</v>
+        <v>58.222</v>
       </c>
       <c r="G3">
         <v>71.3</v>
@@ -1539,28 +1539,28 @@
         <v>112.5</v>
       </c>
       <c r="M3">
-        <v>1.4642833</v>
+        <v>2.9285666</v>
       </c>
       <c r="N3">
-        <v>111.0357167</v>
+        <v>109.5714334</v>
       </c>
       <c r="O3">
-        <v>26.64857200799999</v>
+        <v>26.29714401599999</v>
       </c>
       <c r="P3">
-        <v>84.38714469199998</v>
+        <v>83.27428938399999</v>
       </c>
       <c r="Q3">
-        <v>306.287144692</v>
+        <v>305.174289384</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08598003245981423</v>
+        <v>0.08629238235128291</v>
       </c>
       <c r="T3">
-        <v>0.8261437575906883</v>
+        <v>0.8325660001132414</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>76.82939496749022</v>
+        <v>38.41469748374512</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08533109470425725</v>
+        <v>0.08515967727329843</v>
       </c>
       <c r="C4">
-        <v>2664.568284163705</v>
+        <v>2643.716463781644</v>
       </c>
       <c r="D4">
-        <v>2651.490284163705</v>
+        <v>2659.749463781643</v>
       </c>
       <c r="E4">
-        <v>-838.678</v>
+        <v>-809.567</v>
       </c>
       <c r="F4">
-        <v>58.222</v>
+        <v>87.333</v>
       </c>
       <c r="G4">
         <v>71.3</v>
@@ -1621,28 +1621,28 @@
         <v>112.5</v>
       </c>
       <c r="M4">
-        <v>2.9285666</v>
+        <v>4.3928499</v>
       </c>
       <c r="N4">
-        <v>109.5714334</v>
+        <v>108.1071501</v>
       </c>
       <c r="O4">
-        <v>26.29714401599999</v>
+        <v>25.94571602399999</v>
       </c>
       <c r="P4">
-        <v>83.27428938399999</v>
+        <v>82.16143407599998</v>
       </c>
       <c r="Q4">
-        <v>305.174289384</v>
+        <v>304.061434076</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08629238235128291</v>
+        <v>0.08661117244669941</v>
       </c>
       <c r="T4">
-        <v>0.8325660001132414</v>
+        <v>0.8391206600073939</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>38.41469748374512</v>
+        <v>25.60979832249674</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08515967727329843</v>
+        <v>0.08498825984233961</v>
       </c>
       <c r="C5">
-        <v>2643.716463781644</v>
+        <v>2622.916257537933</v>
       </c>
       <c r="D5">
-        <v>2659.749463781643</v>
+        <v>2668.060257537933</v>
       </c>
       <c r="E5">
-        <v>-809.567</v>
+        <v>-780.456</v>
       </c>
       <c r="F5">
-        <v>87.333</v>
+        <v>116.444</v>
       </c>
       <c r="G5">
         <v>71.3</v>
@@ -1703,28 +1703,28 @@
         <v>112.5</v>
       </c>
       <c r="M5">
-        <v>4.3928499</v>
+        <v>5.8571332</v>
       </c>
       <c r="N5">
-        <v>108.1071501</v>
+        <v>106.6428668</v>
       </c>
       <c r="O5">
-        <v>25.94571602399999</v>
+        <v>25.59428803199999</v>
       </c>
       <c r="P5">
-        <v>82.16143407599998</v>
+        <v>81.04857876799998</v>
       </c>
       <c r="Q5">
-        <v>304.061434076</v>
+        <v>302.948578768</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08661117244669941</v>
+        <v>0.08693660400243711</v>
       </c>
       <c r="T5">
-        <v>0.8391206600073939</v>
+        <v>0.8458118753160079</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>25.60979832249674</v>
+        <v>19.20734874187256</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08498825984233961</v>
+        <v>0.08481684241138078</v>
       </c>
       <c r="C6">
-        <v>2622.916257537933</v>
+        <v>2602.168150777904</v>
       </c>
       <c r="D6">
-        <v>2668.060257537933</v>
+        <v>2676.423150777903</v>
       </c>
       <c r="E6">
-        <v>-780.456</v>
+        <v>-751.345</v>
       </c>
       <c r="F6">
-        <v>116.444</v>
+        <v>145.555</v>
       </c>
       <c r="G6">
         <v>71.3</v>
@@ -1785,28 +1785,28 @@
         <v>112.5</v>
       </c>
       <c r="M6">
-        <v>5.8571332</v>
+        <v>7.3214165</v>
       </c>
       <c r="N6">
-        <v>106.6428668</v>
+        <v>105.1785835</v>
       </c>
       <c r="O6">
-        <v>25.59428803199999</v>
+        <v>25.24286003999999</v>
       </c>
       <c r="P6">
-        <v>81.04857876799998</v>
+        <v>79.93572345999998</v>
       </c>
       <c r="Q6">
-        <v>302.948578768</v>
+        <v>301.83572346</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08693660400243711</v>
+        <v>0.08726888674882188</v>
       </c>
       <c r="T6">
-        <v>0.8458118753160079</v>
+        <v>0.8526439583153294</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>19.20734874187256</v>
+        <v>15.36587899349805</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08481684241138078</v>
+        <v>0.08471382498042197</v>
       </c>
       <c r="C7">
-        <v>2602.168150777904</v>
+        <v>2578.108301075603</v>
       </c>
       <c r="D7">
-        <v>2676.423150777903</v>
+        <v>2681.474301075603</v>
       </c>
       <c r="E7">
-        <v>-751.345</v>
+        <v>-722.2339999999999</v>
       </c>
       <c r="F7">
-        <v>145.555</v>
+        <v>174.666</v>
       </c>
       <c r="G7">
         <v>71.3</v>
@@ -1867,45 +1867,45 @@
         <v>112.5</v>
       </c>
       <c r="M7">
-        <v>7.3214165</v>
+        <v>9.047698799999999</v>
       </c>
       <c r="N7">
-        <v>105.1785835</v>
+        <v>103.4523012</v>
       </c>
       <c r="O7">
-        <v>25.24286003999999</v>
+        <v>24.82855228799999</v>
       </c>
       <c r="P7">
-        <v>79.93572345999998</v>
+        <v>78.62374891199997</v>
       </c>
       <c r="Q7">
-        <v>301.83572346</v>
+        <v>300.523748912</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08726888674882188</v>
+        <v>0.08760823934087444</v>
       </c>
       <c r="T7">
-        <v>0.8526439583153294</v>
+        <v>0.8596214047827215</v>
       </c>
       <c r="U7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V7">
         <v>0.24</v>
       </c>
       <c r="W7">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y7">
-        <v>15.36587899349805</v>
+        <v>12.43410092298828</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08471382498042197</v>
+        <v>0.08455380754946315</v>
       </c>
       <c r="C8">
-        <v>2578.108301075603</v>
+        <v>2556.881194436648</v>
       </c>
       <c r="D8">
-        <v>2681.474301075603</v>
+        <v>2689.358194436648</v>
       </c>
       <c r="E8">
-        <v>-722.2339999999999</v>
+        <v>-693.123</v>
       </c>
       <c r="F8">
-        <v>174.666</v>
+        <v>203.777</v>
       </c>
       <c r="G8">
         <v>71.3</v>
@@ -1949,28 +1949,28 @@
         <v>112.5</v>
       </c>
       <c r="M8">
-        <v>9.047698799999999</v>
+        <v>10.5556486</v>
       </c>
       <c r="N8">
-        <v>103.4523012</v>
+        <v>101.9443514</v>
       </c>
       <c r="O8">
-        <v>24.82855228799999</v>
+        <v>24.46664433599999</v>
       </c>
       <c r="P8">
-        <v>78.62374891199997</v>
+        <v>77.47770706399999</v>
       </c>
       <c r="Q8">
-        <v>300.523748912</v>
+        <v>299.377707064</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08760823934087444</v>
+        <v>0.08795488983813242</v>
       </c>
       <c r="T8">
-        <v>0.8596214047827215</v>
+        <v>0.8667489038623157</v>
       </c>
       <c r="U8">
         <v>0.0518</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>12.43410092298828</v>
+        <v>10.65780079113281</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08455380754946314</v>
+        <v>0.08449715011850432</v>
       </c>
       <c r="C9">
-        <v>2556.881194436649</v>
+        <v>2530.572772243779</v>
       </c>
       <c r="D9">
-        <v>2689.358194436649</v>
+        <v>2692.160772243779</v>
       </c>
       <c r="E9">
-        <v>-693.1229999999999</v>
+        <v>-664.0119999999999</v>
       </c>
       <c r="F9">
-        <v>203.777</v>
+        <v>232.888</v>
       </c>
       <c r="G9">
         <v>71.3</v>
@@ -2031,45 +2031,45 @@
         <v>112.5</v>
       </c>
       <c r="M9">
-        <v>10.5556486</v>
+        <v>12.459508</v>
       </c>
       <c r="N9">
-        <v>101.9443514</v>
+        <v>100.040492</v>
       </c>
       <c r="O9">
-        <v>24.46664433599999</v>
+        <v>24.00971807999999</v>
       </c>
       <c r="P9">
-        <v>77.47770706399999</v>
+        <v>76.03077391999997</v>
       </c>
       <c r="Q9">
-        <v>299.377707064</v>
+        <v>297.93077392</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08795488983813242</v>
+        <v>0.08830907621576557</v>
       </c>
       <c r="T9">
-        <v>0.8667489038623157</v>
+        <v>0.8740313485740749</v>
       </c>
       <c r="U9">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V9">
         <v>0.24</v>
       </c>
       <c r="W9">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>10.65780079113281</v>
+        <v>9.029248988001772</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08449715011850432</v>
+        <v>0.08435005268754553</v>
       </c>
       <c r="C10">
-        <v>2530.572772243779</v>
+        <v>2508.765336136343</v>
       </c>
       <c r="D10">
-        <v>2692.160772243779</v>
+        <v>2699.464336136343</v>
       </c>
       <c r="E10">
-        <v>-664.0119999999999</v>
+        <v>-634.9010000000001</v>
       </c>
       <c r="F10">
-        <v>232.888</v>
+        <v>261.999</v>
       </c>
       <c r="G10">
         <v>71.3</v>
@@ -2113,28 +2113,28 @@
         <v>112.5</v>
       </c>
       <c r="M10">
-        <v>12.459508</v>
+        <v>14.0169465</v>
       </c>
       <c r="N10">
-        <v>100.040492</v>
+        <v>98.48305349999997</v>
       </c>
       <c r="O10">
-        <v>24.00971807999999</v>
+        <v>23.63593283999999</v>
       </c>
       <c r="P10">
-        <v>76.03077391999997</v>
+        <v>74.84712065999997</v>
       </c>
       <c r="Q10">
-        <v>297.93077392</v>
+        <v>296.74712066</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08830907621576557</v>
+        <v>0.08867104690939068</v>
       </c>
       <c r="T10">
-        <v>0.8740313485740749</v>
+        <v>0.881473847015763</v>
       </c>
       <c r="U10">
         <v>0.0535</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>9.029248988001772</v>
+        <v>8.02599910044602</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08435005268754553</v>
+        <v>0.08426375525658669</v>
       </c>
       <c r="C11">
-        <v>2508.765336136343</v>
+        <v>2483.957580183015</v>
       </c>
       <c r="D11">
-        <v>2699.464336136343</v>
+        <v>2703.767580183015</v>
       </c>
       <c r="E11">
-        <v>-634.9010000000001</v>
+        <v>-605.79</v>
       </c>
       <c r="F11">
-        <v>261.999</v>
+        <v>291.11</v>
       </c>
       <c r="G11">
         <v>71.3</v>
@@ -2195,45 +2195,45 @@
         <v>112.5</v>
       </c>
       <c r="M11">
-        <v>14.0169465</v>
+        <v>15.807273</v>
       </c>
       <c r="N11">
-        <v>98.48305349999997</v>
+        <v>96.69272699999998</v>
       </c>
       <c r="O11">
-        <v>23.63593283999999</v>
+        <v>23.20625447999999</v>
       </c>
       <c r="P11">
-        <v>74.84712065999997</v>
+        <v>73.48647251999998</v>
       </c>
       <c r="Q11">
-        <v>296.74712066</v>
+        <v>295.38647252</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08867104690939068</v>
+        <v>0.08904106139620743</v>
       </c>
       <c r="T11">
-        <v>0.881473847015763</v>
+        <v>0.889081734311711</v>
       </c>
       <c r="U11">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V11">
         <v>0.24</v>
       </c>
       <c r="W11">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y11">
-        <v>8.02599910044602</v>
+        <v>7.116977102881692</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08426375525658669</v>
+        <v>0.08412273782562787</v>
       </c>
       <c r="C12">
-        <v>2483.957580183015</v>
+        <v>2461.908055504347</v>
       </c>
       <c r="D12">
-        <v>2703.767580183015</v>
+        <v>2710.829055504347</v>
       </c>
       <c r="E12">
-        <v>-605.79</v>
+        <v>-576.679</v>
       </c>
       <c r="F12">
-        <v>291.11</v>
+        <v>320.221</v>
       </c>
       <c r="G12">
         <v>71.3</v>
@@ -2277,28 +2277,28 @@
         <v>112.5</v>
       </c>
       <c r="M12">
-        <v>15.807273</v>
+        <v>17.3880003</v>
       </c>
       <c r="N12">
-        <v>96.69272699999998</v>
+        <v>95.11199969999997</v>
       </c>
       <c r="O12">
-        <v>23.20625447999999</v>
+        <v>22.82687992799999</v>
       </c>
       <c r="P12">
-        <v>73.48647251999998</v>
+        <v>72.28511977199997</v>
       </c>
       <c r="Q12">
-        <v>295.38647252</v>
+        <v>294.185119772</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08904106139620743</v>
+        <v>0.08941939081531222</v>
       </c>
       <c r="T12">
-        <v>0.889081734311711</v>
+        <v>0.8968605853671183</v>
       </c>
       <c r="U12">
         <v>0.0543</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>7.116977102881691</v>
+        <v>6.4699791844379</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08412273782562787</v>
+        <v>0.08407292039466904</v>
       </c>
       <c r="C13">
-        <v>2461.908055504347</v>
+        <v>2435.300498085982</v>
       </c>
       <c r="D13">
-        <v>2710.829055504347</v>
+        <v>2713.332498085982</v>
       </c>
       <c r="E13">
-        <v>-576.679</v>
+        <v>-547.568</v>
       </c>
       <c r="F13">
-        <v>320.221</v>
+        <v>349.332</v>
       </c>
       <c r="G13">
         <v>71.3</v>
@@ -2359,45 +2359,45 @@
         <v>112.5</v>
       </c>
       <c r="M13">
-        <v>17.3880003</v>
+        <v>19.3180596</v>
       </c>
       <c r="N13">
-        <v>95.11199969999997</v>
+        <v>93.18194039999997</v>
       </c>
       <c r="O13">
-        <v>22.82687992799999</v>
+        <v>22.36366569599999</v>
       </c>
       <c r="P13">
-        <v>72.28511977199997</v>
+        <v>70.81827470399998</v>
       </c>
       <c r="Q13">
-        <v>294.185119772</v>
+        <v>292.718274704</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08941939081531222</v>
+        <v>0.08980631863030573</v>
       </c>
       <c r="T13">
-        <v>0.8968605853671183</v>
+        <v>0.9048162284919665</v>
       </c>
       <c r="U13">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V13">
         <v>0.24</v>
       </c>
       <c r="W13">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y13">
-        <v>6.4699791844379</v>
+        <v>5.823566255070461</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08407292039466904</v>
+        <v>0.08393950296371024</v>
       </c>
       <c r="C14">
-        <v>2435.300498085982</v>
+        <v>2412.916866501355</v>
       </c>
       <c r="D14">
-        <v>2713.332498085982</v>
+        <v>2720.059866501354</v>
       </c>
       <c r="E14">
-        <v>-547.568</v>
+        <v>-518.457</v>
       </c>
       <c r="F14">
-        <v>349.332</v>
+        <v>378.443</v>
       </c>
       <c r="G14">
         <v>71.3</v>
@@ -2441,28 +2441,28 @@
         <v>112.5</v>
       </c>
       <c r="M14">
-        <v>19.3180596</v>
+        <v>20.9278979</v>
       </c>
       <c r="N14">
-        <v>93.18194039999997</v>
+        <v>91.57210209999997</v>
       </c>
       <c r="O14">
-        <v>22.36366569599999</v>
+        <v>21.97730450399999</v>
       </c>
       <c r="P14">
-        <v>70.81827470399998</v>
+        <v>69.59479759599998</v>
       </c>
       <c r="Q14">
-        <v>292.718274704</v>
+        <v>291.494797596</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08980631863030573</v>
+        <v>0.09020214133759796</v>
       </c>
       <c r="T14">
-        <v>0.9048162284919665</v>
+        <v>0.9129547599645127</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.823566255070461</v>
+        <v>5.37559962006504</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08393950296371024</v>
+        <v>0.08380608553275141</v>
       </c>
       <c r="C15">
-        <v>2412.916866501355</v>
+        <v>2390.566677169017</v>
       </c>
       <c r="D15">
-        <v>2720.059866501354</v>
+        <v>2726.820677169017</v>
       </c>
       <c r="E15">
-        <v>-518.457</v>
+        <v>-489.3459999999999</v>
       </c>
       <c r="F15">
-        <v>378.443</v>
+        <v>407.554</v>
       </c>
       <c r="G15">
         <v>71.3</v>
@@ -2523,28 +2523,28 @@
         <v>112.5</v>
       </c>
       <c r="M15">
-        <v>20.9278979</v>
+        <v>22.5377362</v>
       </c>
       <c r="N15">
-        <v>91.57210209999997</v>
+        <v>89.96226379999997</v>
       </c>
       <c r="O15">
-        <v>21.97730450399999</v>
+        <v>21.59094331199999</v>
       </c>
       <c r="P15">
-        <v>69.59479759599998</v>
+        <v>68.37132048799998</v>
       </c>
       <c r="Q15">
-        <v>291.494797596</v>
+        <v>290.271320488</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09020214133759796</v>
+        <v>0.09060716922412955</v>
       </c>
       <c r="T15">
-        <v>0.9129547599645127</v>
+        <v>0.9212825596108388</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.37559962006504</v>
+        <v>4.991628218631824</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08380608553275141</v>
+        <v>0.08367266810179259</v>
       </c>
       <c r="C16">
-        <v>2390.566677169017</v>
+        <v>2368.250180076232</v>
       </c>
       <c r="D16">
-        <v>2726.820677169017</v>
+        <v>2733.615180076231</v>
       </c>
       <c r="E16">
-        <v>-489.3459999999999</v>
+        <v>-460.2349999999999</v>
       </c>
       <c r="F16">
-        <v>407.554</v>
+        <v>436.6650000000001</v>
       </c>
       <c r="G16">
         <v>71.3</v>
@@ -2605,28 +2605,28 @@
         <v>112.5</v>
       </c>
       <c r="M16">
-        <v>22.5377362</v>
+        <v>24.1475745</v>
       </c>
       <c r="N16">
-        <v>89.96226379999997</v>
+        <v>88.35242549999997</v>
       </c>
       <c r="O16">
-        <v>21.59094331199999</v>
+        <v>21.20458211999999</v>
       </c>
       <c r="P16">
-        <v>68.37132048799998</v>
+        <v>67.14784337999998</v>
       </c>
       <c r="Q16">
-        <v>290.271320488</v>
+        <v>289.04784338</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09060716922412955</v>
+        <v>0.09102172717857952</v>
       </c>
       <c r="T16">
-        <v>0.9212825596108388</v>
+        <v>0.9298063074841375</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>4.991628218631824</v>
+        <v>4.658853004056368</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08367266810179259</v>
+        <v>0.08384325067083379</v>
       </c>
       <c r="C17">
-        <v>2368.250180076232</v>
+        <v>2330.457991829624</v>
       </c>
       <c r="D17">
-        <v>2733.615180076231</v>
+        <v>2724.933991829624</v>
       </c>
       <c r="E17">
-        <v>-460.235</v>
+        <v>-431.124</v>
       </c>
       <c r="F17">
-        <v>436.665</v>
+        <v>465.776</v>
       </c>
       <c r="G17">
         <v>71.3</v>
@@ -2687,45 +2687,45 @@
         <v>112.5</v>
       </c>
       <c r="M17">
-        <v>24.1475745</v>
+        <v>26.9218528</v>
       </c>
       <c r="N17">
-        <v>88.35242549999998</v>
+        <v>85.57814719999996</v>
       </c>
       <c r="O17">
-        <v>21.20458211999999</v>
+        <v>20.53875532799999</v>
       </c>
       <c r="P17">
-        <v>67.14784337999998</v>
+        <v>65.03939187199997</v>
       </c>
       <c r="Q17">
-        <v>289.04784338</v>
+        <v>286.939391872</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09102172717857952</v>
+        <v>0.09144615556051641</v>
       </c>
       <c r="T17">
-        <v>0.9298063074841374</v>
+        <v>0.9385330017353718</v>
       </c>
       <c r="U17">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V17">
         <v>0.24</v>
       </c>
       <c r="W17">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y17">
-        <v>4.65885300405637</v>
+        <v>4.178761426108085</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08384325067083379</v>
+        <v>0.08418103323987497</v>
       </c>
       <c r="C18">
-        <v>2330.457991829624</v>
+        <v>2284.318433799734</v>
       </c>
       <c r="D18">
-        <v>2724.933991829624</v>
+        <v>2707.905433799734</v>
       </c>
       <c r="E18">
-        <v>-431.124</v>
+        <v>-402.013</v>
       </c>
       <c r="F18">
-        <v>465.776</v>
+        <v>494.887</v>
       </c>
       <c r="G18">
         <v>71.3</v>
@@ -2769,45 +2769,45 @@
         <v>112.5</v>
       </c>
       <c r="M18">
-        <v>26.9218528</v>
+        <v>30.3365731</v>
       </c>
       <c r="N18">
-        <v>85.57814719999996</v>
+        <v>82.16342689999998</v>
       </c>
       <c r="O18">
-        <v>20.53875532799999</v>
+        <v>19.71922245599999</v>
       </c>
       <c r="P18">
-        <v>65.03939187199997</v>
+        <v>62.44420444399998</v>
       </c>
       <c r="Q18">
-        <v>286.939391872</v>
+        <v>284.344204444</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09144615556051641</v>
+        <v>0.09188081113237948</v>
       </c>
       <c r="T18">
-        <v>0.9385330017353718</v>
+        <v>0.9474699777757923</v>
       </c>
       <c r="U18">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V18">
         <v>0.24</v>
       </c>
       <c r="W18">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>4.178761426108085</v>
+        <v>3.708395131815333</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08418103323987497</v>
+        <v>0.08409321580891613</v>
       </c>
       <c r="C19">
-        <v>2284.318433799734</v>
+        <v>2259.61404804219</v>
       </c>
       <c r="D19">
-        <v>2707.905433799734</v>
+        <v>2712.31204804219</v>
       </c>
       <c r="E19">
-        <v>-402.013</v>
+        <v>-372.9019999999999</v>
       </c>
       <c r="F19">
-        <v>494.887</v>
+        <v>523.998</v>
       </c>
       <c r="G19">
         <v>71.3</v>
@@ -2851,28 +2851,28 @@
         <v>112.5</v>
       </c>
       <c r="M19">
-        <v>30.3365731</v>
+        <v>32.1210774</v>
       </c>
       <c r="N19">
-        <v>82.16342689999998</v>
+        <v>80.37892259999997</v>
       </c>
       <c r="O19">
-        <v>19.71922245599999</v>
+        <v>19.29094142399999</v>
       </c>
       <c r="P19">
-        <v>62.44420444399998</v>
+        <v>61.08798117599997</v>
       </c>
       <c r="Q19">
-        <v>284.344204444</v>
+        <v>282.9879811759999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09188081113237948</v>
+        <v>0.09232606805965382</v>
       </c>
       <c r="T19">
-        <v>0.9474699777757923</v>
+        <v>0.9566249288415891</v>
       </c>
       <c r="U19">
         <v>0.0613</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.708395131815333</v>
+        <v>3.502373180047814</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08409321580891613</v>
+        <v>0.0844097183779573</v>
       </c>
       <c r="C20">
-        <v>2259.61404804219</v>
+        <v>2214.688091320818</v>
       </c>
       <c r="D20">
-        <v>2712.31204804219</v>
+        <v>2696.497091320818</v>
       </c>
       <c r="E20">
-        <v>-372.902</v>
+        <v>-343.7909999999999</v>
       </c>
       <c r="F20">
-        <v>523.9979999999999</v>
+        <v>553.109</v>
       </c>
       <c r="G20">
         <v>71.3</v>
@@ -2933,45 +2933,45 @@
         <v>112.5</v>
       </c>
       <c r="M20">
-        <v>32.1210774</v>
+        <v>35.45428690000001</v>
       </c>
       <c r="N20">
-        <v>80.37892259999998</v>
+        <v>77.04571309999997</v>
       </c>
       <c r="O20">
-        <v>19.290941424</v>
+        <v>18.49097114399999</v>
       </c>
       <c r="P20">
-        <v>61.08798117599999</v>
+        <v>58.55474195599998</v>
       </c>
       <c r="Q20">
-        <v>282.987981176</v>
+        <v>280.454741956</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09232606805965382</v>
+        <v>0.09278231898513248</v>
       </c>
       <c r="T20">
-        <v>0.9566249288415889</v>
+        <v>0.9660059280818498</v>
       </c>
       <c r="U20">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V20">
         <v>0.24</v>
       </c>
       <c r="W20">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y20">
-        <v>3.502373180047814</v>
+        <v>3.173100063112536</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0844097183779573</v>
+        <v>0.0843431809469985</v>
       </c>
       <c r="C21">
-        <v>2214.688091320818</v>
+        <v>2188.886495275592</v>
       </c>
       <c r="D21">
-        <v>2696.497091320818</v>
+        <v>2699.806495275592</v>
       </c>
       <c r="E21">
-        <v>-343.7909999999999</v>
+        <v>-314.6799999999999</v>
       </c>
       <c r="F21">
-        <v>553.109</v>
+        <v>582.22</v>
       </c>
       <c r="G21">
         <v>71.3</v>
@@ -3015,28 +3015,28 @@
         <v>112.5</v>
       </c>
       <c r="M21">
-        <v>35.45428690000001</v>
+        <v>37.32030200000001</v>
       </c>
       <c r="N21">
-        <v>77.04571309999997</v>
+        <v>75.17969799999997</v>
       </c>
       <c r="O21">
-        <v>18.49097114399999</v>
+        <v>18.04312751999999</v>
       </c>
       <c r="P21">
-        <v>58.55474195599998</v>
+        <v>57.13657047999998</v>
       </c>
       <c r="Q21">
-        <v>280.454741956</v>
+        <v>279.03657048</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09278231898513248</v>
+        <v>0.09324997618374811</v>
       </c>
       <c r="T21">
-        <v>0.9660059280818498</v>
+        <v>0.9756214523031171</v>
       </c>
       <c r="U21">
         <v>0.0641</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.173100063112536</v>
+        <v>3.014445059956909</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0843431809469985</v>
+        <v>0.08552152351603967</v>
       </c>
       <c r="C22">
-        <v>2188.886495275592</v>
+        <v>2102.344039818442</v>
       </c>
       <c r="D22">
-        <v>2699.806495275592</v>
+        <v>2642.375039818442</v>
       </c>
       <c r="E22">
-        <v>-314.6799999999999</v>
+        <v>-285.569</v>
       </c>
       <c r="F22">
-        <v>582.22</v>
+        <v>611.331</v>
       </c>
       <c r="G22">
         <v>71.3</v>
@@ -3097,45 +3097,45 @@
         <v>112.5</v>
       </c>
       <c r="M22">
-        <v>37.32030200000001</v>
+        <v>43.9546989</v>
       </c>
       <c r="N22">
-        <v>75.17969799999997</v>
+        <v>68.54530109999996</v>
       </c>
       <c r="O22">
-        <v>18.04312751999999</v>
+        <v>16.45087226399999</v>
       </c>
       <c r="P22">
-        <v>57.13657047999998</v>
+        <v>52.09442883599997</v>
       </c>
       <c r="Q22">
-        <v>279.03657048</v>
+        <v>273.994428836</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09324997618374811</v>
+        <v>0.09372947280511351</v>
       </c>
       <c r="T22">
-        <v>0.9756214523031171</v>
+        <v>0.985480407517328</v>
       </c>
       <c r="U22">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V22">
         <v>0.24</v>
       </c>
       <c r="W22">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>3.014445059956909</v>
+        <v>2.559453319335557</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08552152351603967</v>
+        <v>0.08616634608508086</v>
       </c>
       <c r="C23">
-        <v>2102.344039818442</v>
+        <v>2042.827414879481</v>
       </c>
       <c r="D23">
-        <v>2642.375039818442</v>
+        <v>2611.969414879481</v>
       </c>
       <c r="E23">
-        <v>-285.5690000000001</v>
+        <v>-256.458</v>
       </c>
       <c r="F23">
-        <v>611.3309999999999</v>
+        <v>640.442</v>
       </c>
       <c r="G23">
         <v>71.3</v>
@@ -3179,45 +3179,45 @@
         <v>112.5</v>
       </c>
       <c r="M23">
-        <v>43.9546989</v>
+        <v>48.5455036</v>
       </c>
       <c r="N23">
-        <v>68.54530109999997</v>
+        <v>63.95449639999997</v>
       </c>
       <c r="O23">
-        <v>16.45087226399999</v>
+        <v>15.34907913599999</v>
       </c>
       <c r="P23">
-        <v>52.09442883599998</v>
+        <v>48.60541726399997</v>
       </c>
       <c r="Q23">
-        <v>273.994428836</v>
+        <v>270.505417264</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09372947280511351</v>
+        <v>0.09422126421164212</v>
       </c>
       <c r="T23">
-        <v>0.985480407517328</v>
+        <v>0.9955921564549802</v>
       </c>
       <c r="U23">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V23">
         <v>0.24</v>
       </c>
       <c r="W23">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y23">
-        <v>2.559453319335558</v>
+        <v>2.317413388621227</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08616634608508086</v>
+        <v>0.08618872865412204</v>
       </c>
       <c r="C24">
-        <v>2042.827414879481</v>
+        <v>2012.673560101614</v>
       </c>
       <c r="D24">
-        <v>2611.969414879481</v>
+        <v>2610.926560101614</v>
       </c>
       <c r="E24">
-        <v>-256.458</v>
+        <v>-227.347</v>
       </c>
       <c r="F24">
-        <v>640.442</v>
+        <v>669.553</v>
       </c>
       <c r="G24">
         <v>71.3</v>
@@ -3261,28 +3261,28 @@
         <v>112.5</v>
       </c>
       <c r="M24">
-        <v>48.5455036</v>
+        <v>50.7521174</v>
       </c>
       <c r="N24">
-        <v>63.95449639999997</v>
+        <v>61.74788259999997</v>
       </c>
       <c r="O24">
-        <v>15.34907913599999</v>
+        <v>14.81949182399999</v>
       </c>
       <c r="P24">
-        <v>48.60541726399997</v>
+        <v>46.92839077599998</v>
       </c>
       <c r="Q24">
-        <v>270.505417264</v>
+        <v>268.828390776</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09422126421164212</v>
+        <v>0.09472582942093771</v>
       </c>
       <c r="T24">
-        <v>0.9955921564549802</v>
+        <v>1.005966548222182</v>
       </c>
       <c r="U24">
         <v>0.07580000000000001</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.317413388621227</v>
+        <v>2.21665628476813</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08618872865412204</v>
+        <v>0.08621111122316322</v>
       </c>
       <c r="C25">
-        <v>2012.673560101614</v>
+        <v>1982.520537731692</v>
       </c>
       <c r="D25">
-        <v>2610.926560101614</v>
+        <v>2609.884537731692</v>
       </c>
       <c r="E25">
-        <v>-227.347</v>
+        <v>-198.236</v>
       </c>
       <c r="F25">
-        <v>669.553</v>
+        <v>698.664</v>
       </c>
       <c r="G25">
         <v>71.3</v>
@@ -3343,28 +3343,28 @@
         <v>112.5</v>
       </c>
       <c r="M25">
-        <v>50.7521174</v>
+        <v>52.9587312</v>
       </c>
       <c r="N25">
-        <v>61.74788259999997</v>
+        <v>59.54126879999997</v>
       </c>
       <c r="O25">
-        <v>14.81949182399999</v>
+        <v>14.28990451199999</v>
       </c>
       <c r="P25">
-        <v>46.92839077599998</v>
+        <v>45.25136428799998</v>
       </c>
       <c r="Q25">
-        <v>268.828390776</v>
+        <v>267.151364288</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09472582942093771</v>
+        <v>0.09524367266205686</v>
       </c>
       <c r="T25">
-        <v>1.005966548222182</v>
+        <v>1.016613950299047</v>
       </c>
       <c r="U25">
         <v>0.07580000000000001</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.21665628476813</v>
+        <v>2.124295606236124</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08621111122316322</v>
+        <v>0.08623349379220441</v>
       </c>
       <c r="C26">
-        <v>1982.520537731692</v>
+        <v>1952.36834677347</v>
       </c>
       <c r="D26">
-        <v>2609.884537731692</v>
+        <v>2608.843346773469</v>
       </c>
       <c r="E26">
-        <v>-198.236</v>
+        <v>-169.125</v>
       </c>
       <c r="F26">
-        <v>698.664</v>
+        <v>727.775</v>
       </c>
       <c r="G26">
         <v>71.3</v>
@@ -3425,28 +3425,28 @@
         <v>112.5</v>
       </c>
       <c r="M26">
-        <v>52.9587312</v>
+        <v>55.165345</v>
       </c>
       <c r="N26">
-        <v>59.54126879999997</v>
+        <v>57.33465499999997</v>
       </c>
       <c r="O26">
-        <v>14.28990451199999</v>
+        <v>13.76031719999999</v>
       </c>
       <c r="P26">
-        <v>45.25136428799998</v>
+        <v>43.57433779999998</v>
       </c>
       <c r="Q26">
-        <v>267.151364288</v>
+        <v>265.4743378</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09524367266205686</v>
+        <v>0.09577532505627254</v>
       </c>
       <c r="T26">
-        <v>1.016613950299047</v>
+        <v>1.027545283097961</v>
       </c>
       <c r="U26">
         <v>0.07580000000000001</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.124295606236124</v>
+        <v>2.039323781986679</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08623349379220441</v>
+        <v>0.08906179636124556</v>
       </c>
       <c r="C27">
-        <v>1952.36834677347</v>
+        <v>1798.05462122842</v>
       </c>
       <c r="D27">
-        <v>2608.843346773469</v>
+        <v>2483.64062122842</v>
       </c>
       <c r="E27">
-        <v>-169.125</v>
+        <v>-140.014</v>
       </c>
       <c r="F27">
-        <v>727.775</v>
+        <v>756.886</v>
       </c>
       <c r="G27">
         <v>71.3</v>
@@ -3507,45 +3507,45 @@
         <v>112.5</v>
       </c>
       <c r="M27">
-        <v>55.165345</v>
+        <v>68.11973999999999</v>
       </c>
       <c r="N27">
-        <v>57.33465499999997</v>
+        <v>44.38025999999998</v>
       </c>
       <c r="O27">
-        <v>13.76031719999999</v>
+        <v>10.65126239999999</v>
       </c>
       <c r="P27">
-        <v>43.57433779999998</v>
+        <v>33.72899759999999</v>
       </c>
       <c r="Q27">
-        <v>265.4743378</v>
+        <v>255.6289976</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09577532505627254</v>
+        <v>0.09632134643411563</v>
       </c>
       <c r="T27">
-        <v>1.027545283097961</v>
+        <v>1.038772057323873</v>
       </c>
       <c r="U27">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V27">
         <v>0.24</v>
       </c>
       <c r="W27">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y27">
-        <v>2.039323781986679</v>
+        <v>1.651503661053316</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08906179636124556</v>
+        <v>0.08919209893028675</v>
       </c>
       <c r="C28">
-        <v>1798.05462122842</v>
+        <v>1763.464354127632</v>
       </c>
       <c r="D28">
-        <v>2483.64062122842</v>
+        <v>2478.161354127632</v>
       </c>
       <c r="E28">
-        <v>-140.014</v>
+        <v>-110.9029999999999</v>
       </c>
       <c r="F28">
-        <v>756.886</v>
+        <v>785.9970000000001</v>
       </c>
       <c r="G28">
         <v>71.3</v>
@@ -3589,28 +3589,28 @@
         <v>112.5</v>
       </c>
       <c r="M28">
-        <v>68.11973999999999</v>
+        <v>70.73973000000001</v>
       </c>
       <c r="N28">
-        <v>44.38025999999998</v>
+        <v>41.76026999999996</v>
       </c>
       <c r="O28">
-        <v>10.65126239999999</v>
+        <v>10.02246479999999</v>
       </c>
       <c r="P28">
-        <v>33.72899759999999</v>
+        <v>31.73780519999997</v>
       </c>
       <c r="Q28">
-        <v>255.6289976</v>
+        <v>253.6378052</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09632134643411563</v>
+        <v>0.09688232730176267</v>
       </c>
       <c r="T28">
-        <v>1.038772057323873</v>
+        <v>1.05030641440529</v>
       </c>
       <c r="U28">
         <v>0.09</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>1.651503661053316</v>
+        <v>1.590336858792081</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08919209893028675</v>
+        <v>0.08932240149932794</v>
       </c>
       <c r="C29">
-        <v>1763.464354127632</v>
+        <v>1728.898209905056</v>
       </c>
       <c r="D29">
-        <v>2478.161354127632</v>
+        <v>2472.706209905056</v>
       </c>
       <c r="E29">
-        <v>-110.9029999999999</v>
+        <v>-81.79199999999992</v>
       </c>
       <c r="F29">
-        <v>785.9970000000001</v>
+        <v>815.1080000000001</v>
       </c>
       <c r="G29">
         <v>71.3</v>
@@ -3671,28 +3671,28 @@
         <v>112.5</v>
       </c>
       <c r="M29">
-        <v>70.73973000000001</v>
+        <v>73.35972</v>
       </c>
       <c r="N29">
-        <v>41.76026999999996</v>
+        <v>39.14027999999998</v>
       </c>
       <c r="O29">
-        <v>10.02246479999999</v>
+        <v>9.393667199999994</v>
       </c>
       <c r="P29">
-        <v>31.73780519999997</v>
+        <v>29.74661279999998</v>
       </c>
       <c r="Q29">
-        <v>253.6378052</v>
+        <v>251.6466128</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09688232730176267</v>
+        <v>0.09745889097128879</v>
       </c>
       <c r="T29">
-        <v>1.05030641440529</v>
+        <v>1.062161170294524</v>
       </c>
       <c r="U29">
         <v>0.09</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>1.590336858792081</v>
+        <v>1.533539113835221</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08932240149932794</v>
+        <v>0.1031698445510563</v>
       </c>
       <c r="C30">
-        <v>1728.898209905056</v>
+        <v>1231.002033726147</v>
       </c>
       <c r="D30">
-        <v>2472.706209905056</v>
+        <v>2003.921033726147</v>
       </c>
       <c r="E30">
-        <v>-81.79199999999992</v>
+        <v>-52.68099999999993</v>
       </c>
       <c r="F30">
-        <v>815.1080000000001</v>
+        <v>844.2190000000001</v>
       </c>
       <c r="G30">
         <v>71.3</v>
@@ -3753,45 +3753,45 @@
         <v>112.5</v>
       </c>
       <c r="M30">
-        <v>73.35972</v>
+        <v>123.9313492</v>
       </c>
       <c r="N30">
-        <v>39.14027999999998</v>
+        <v>-11.43134920000004</v>
       </c>
       <c r="O30">
-        <v>9.393667199999994</v>
+        <v>-2.74352380800001</v>
       </c>
       <c r="P30">
-        <v>29.74661279999998</v>
+        <v>-8.687825392000033</v>
       </c>
       <c r="Q30">
-        <v>251.6466128</v>
+        <v>213.212174608</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09745889097128879</v>
+        <v>0.09841223818525593</v>
       </c>
       <c r="T30">
-        <v>1.062161170294524</v>
+        <v>1.081762992429016</v>
       </c>
       <c r="U30">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V30">
-        <v>0.24</v>
+        <v>0.2178625519232223</v>
       </c>
       <c r="W30">
-        <v>0.0684</v>
+        <v>0.114817777377671</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y30">
-        <v>1.533539113835221</v>
+        <v>0.9077606330134261</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1031698445510563</v>
+        <v>0.1041798445510563</v>
       </c>
       <c r="C31">
-        <v>1231.002033726148</v>
+        <v>1174.559151294638</v>
       </c>
       <c r="D31">
-        <v>2003.921033726147</v>
+        <v>1976.589151294638</v>
       </c>
       <c r="E31">
-        <v>-52.68100000000004</v>
+        <v>-23.57000000000005</v>
       </c>
       <c r="F31">
-        <v>844.2189999999999</v>
+        <v>873.3299999999999</v>
       </c>
       <c r="G31">
         <v>71.3</v>
@@ -3835,37 +3835,37 @@
         <v>112.5</v>
       </c>
       <c r="M31">
-        <v>123.9313492</v>
+        <v>128.204844</v>
       </c>
       <c r="N31">
-        <v>-11.43134920000003</v>
+        <v>-15.70484400000004</v>
       </c>
       <c r="O31">
-        <v>-2.743523808000007</v>
+        <v>-3.769162560000009</v>
       </c>
       <c r="P31">
-        <v>-8.687825392000022</v>
+        <v>-11.93568144000003</v>
       </c>
       <c r="Q31">
-        <v>213.212174608</v>
+        <v>209.96431856</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09841223818525593</v>
+        <v>0.09916384158790245</v>
       </c>
       <c r="T31">
-        <v>1.081762992429016</v>
+        <v>1.097216749463717</v>
       </c>
       <c r="U31">
         <v>0.1468</v>
       </c>
       <c r="V31">
-        <v>0.2178625519232223</v>
+        <v>0.2106004668591149</v>
       </c>
       <c r="W31">
-        <v>0.114817777377671</v>
+        <v>0.115883851465082</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.9077606330134262</v>
+        <v>0.877501945246312</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1041798445510563</v>
+        <v>0.1051898445510563</v>
       </c>
       <c r="C32">
-        <v>1174.559151294638</v>
+        <v>1118.851806807525</v>
       </c>
       <c r="D32">
-        <v>1976.589151294638</v>
+        <v>1949.992806807525</v>
       </c>
       <c r="E32">
-        <v>-23.57000000000005</v>
+        <v>5.54099999999994</v>
       </c>
       <c r="F32">
-        <v>873.3299999999999</v>
+        <v>902.4409999999999</v>
       </c>
       <c r="G32">
         <v>71.3</v>
@@ -3917,37 +3917,37 @@
         <v>112.5</v>
       </c>
       <c r="M32">
-        <v>128.204844</v>
+        <v>132.4783388</v>
       </c>
       <c r="N32">
-        <v>-15.70484400000004</v>
+        <v>-19.97833880000002</v>
       </c>
       <c r="O32">
-        <v>-3.769162560000009</v>
+        <v>-4.794801312000004</v>
       </c>
       <c r="P32">
-        <v>-11.93568144000003</v>
+        <v>-15.18353748800001</v>
       </c>
       <c r="Q32">
-        <v>209.96431856</v>
+        <v>206.716462512</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09916384158790245</v>
+        <v>0.09993723059642279</v>
       </c>
       <c r="T32">
-        <v>1.097216749463717</v>
+        <v>1.11311844148493</v>
       </c>
       <c r="U32">
         <v>0.1468</v>
       </c>
       <c r="V32">
-        <v>0.2106004668591149</v>
+        <v>0.2038069034120467</v>
       </c>
       <c r="W32">
-        <v>0.115883851465082</v>
+        <v>0.1168811465791116</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.877501945246312</v>
+        <v>0.8491954308835278</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1051898445510563</v>
+        <v>0.1061998445510563</v>
       </c>
       <c r="C33">
-        <v>1118.851806807525</v>
+        <v>1063.850702997139</v>
       </c>
       <c r="D33">
-        <v>1949.992806807525</v>
+        <v>1924.102702997139</v>
       </c>
       <c r="E33">
-        <v>5.54099999999994</v>
+        <v>34.65200000000004</v>
       </c>
       <c r="F33">
-        <v>902.4409999999999</v>
+        <v>931.552</v>
       </c>
       <c r="G33">
         <v>71.3</v>
@@ -3999,37 +3999,37 @@
         <v>112.5</v>
       </c>
       <c r="M33">
-        <v>132.4783388</v>
+        <v>136.7518336</v>
       </c>
       <c r="N33">
-        <v>-19.97833880000002</v>
+        <v>-24.25183360000005</v>
       </c>
       <c r="O33">
-        <v>-4.794801312000004</v>
+        <v>-5.820440064000013</v>
       </c>
       <c r="P33">
-        <v>-15.18353748800001</v>
+        <v>-18.43139353600004</v>
       </c>
       <c r="Q33">
-        <v>206.716462512</v>
+        <v>203.468606464</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09993723059642279</v>
+        <v>0.1007333663404878</v>
       </c>
       <c r="T33">
-        <v>1.11311844148493</v>
+        <v>1.129487830330297</v>
       </c>
       <c r="U33">
         <v>0.1468</v>
       </c>
       <c r="V33">
-        <v>0.2038069034120467</v>
+        <v>0.1974379376804202</v>
       </c>
       <c r="W33">
-        <v>0.1168811465791116</v>
+        <v>0.1178161107485143</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.8491954308835278</v>
+        <v>0.8226580736684174</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1061998445510563</v>
+        <v>0.1257073295338787</v>
       </c>
       <c r="C34">
-        <v>1063.850702997139</v>
+        <v>642.03308336549</v>
       </c>
       <c r="D34">
-        <v>1924.102702997139</v>
+        <v>1531.39608336549</v>
       </c>
       <c r="E34">
-        <v>34.65200000000004</v>
+        <v>63.76300000000003</v>
       </c>
       <c r="F34">
-        <v>931.552</v>
+        <v>960.663</v>
       </c>
       <c r="G34">
         <v>71.3</v>
@@ -4081,45 +4081,45 @@
         <v>112.5</v>
       </c>
       <c r="M34">
-        <v>136.7518336</v>
+        <v>192.9011304</v>
       </c>
       <c r="N34">
-        <v>-24.25183360000005</v>
+        <v>-80.40113040000003</v>
       </c>
       <c r="O34">
-        <v>-5.820440064000013</v>
+        <v>-19.29627129600001</v>
       </c>
       <c r="P34">
-        <v>-18.43139353600004</v>
+        <v>-61.10485910400002</v>
       </c>
       <c r="Q34">
-        <v>203.468606464</v>
+        <v>160.795140896</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1007333663404878</v>
+        <v>0.1025644389467971</v>
       </c>
       <c r="T34">
-        <v>1.129487830330297</v>
+        <v>1.167136610353327</v>
       </c>
       <c r="U34">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V34">
-        <v>0.1974379376804202</v>
+        <v>0.1399680755836566</v>
       </c>
       <c r="W34">
-        <v>0.1178161107485143</v>
+        <v>0.1726944104228018</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y34">
-        <v>0.8226580736684174</v>
+        <v>0.5832003149319024</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1257073295338787</v>
+        <v>0.1272573295338787</v>
       </c>
       <c r="C35">
-        <v>642.03308336549</v>
+        <v>588.483756601723</v>
       </c>
       <c r="D35">
-        <v>1531.39608336549</v>
+        <v>1506.957756601723</v>
       </c>
       <c r="E35">
-        <v>63.76300000000003</v>
+        <v>92.87400000000002</v>
       </c>
       <c r="F35">
-        <v>960.663</v>
+        <v>989.774</v>
       </c>
       <c r="G35">
         <v>71.3</v>
@@ -4163,37 +4163,37 @@
         <v>112.5</v>
       </c>
       <c r="M35">
-        <v>192.9011304</v>
+        <v>198.7466192</v>
       </c>
       <c r="N35">
-        <v>-80.40113040000003</v>
+        <v>-86.24661920000003</v>
       </c>
       <c r="O35">
-        <v>-19.29627129600001</v>
+        <v>-20.69918860800001</v>
       </c>
       <c r="P35">
-        <v>-61.10485910400002</v>
+        <v>-65.54743059200001</v>
       </c>
       <c r="Q35">
-        <v>160.795140896</v>
+        <v>156.352569408</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1025644389467971</v>
+        <v>0.1034245062035668</v>
       </c>
       <c r="T35">
-        <v>1.167136610353327</v>
+        <v>1.184820498388983</v>
       </c>
       <c r="U35">
         <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.1399680755836566</v>
+        <v>0.1358513674782549</v>
       </c>
       <c r="W35">
-        <v>0.1726944104228018</v>
+        <v>0.1735210454103664</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.5832003149319024</v>
+        <v>0.5660473644927289</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1272573295338787</v>
+        <v>0.1288073295338787</v>
       </c>
       <c r="C36">
-        <v>588.483756601723</v>
+        <v>535.7021616879834</v>
       </c>
       <c r="D36">
-        <v>1506.957756601723</v>
+        <v>1483.287161687984</v>
       </c>
       <c r="E36">
-        <v>92.87400000000002</v>
+        <v>121.9850000000001</v>
       </c>
       <c r="F36">
-        <v>989.774</v>
+        <v>1018.885</v>
       </c>
       <c r="G36">
         <v>71.3</v>
@@ -4245,37 +4245,37 @@
         <v>112.5</v>
       </c>
       <c r="M36">
-        <v>198.7466192</v>
+        <v>204.592108</v>
       </c>
       <c r="N36">
-        <v>-86.24661920000003</v>
+        <v>-92.09210800000005</v>
       </c>
       <c r="O36">
-        <v>-20.69918860800001</v>
+        <v>-22.10210592000001</v>
       </c>
       <c r="P36">
-        <v>-65.54743059200001</v>
+        <v>-69.99000208000004</v>
       </c>
       <c r="Q36">
-        <v>156.352569408</v>
+        <v>151.90999792</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1034245062035668</v>
+        <v>0.1043110370682371</v>
       </c>
       <c r="T36">
-        <v>1.184820498388983</v>
+        <v>1.203048506056506</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.1358513674782549</v>
+        <v>0.131969899836019</v>
       </c>
       <c r="W36">
-        <v>0.1735210454103664</v>
+        <v>0.1743004441129274</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.5660473644927289</v>
+        <v>0.5498745826500793</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1288073295338787</v>
+        <v>0.1303573295338787</v>
       </c>
       <c r="C37">
-        <v>535.7021616879834</v>
+        <v>483.6526805666169</v>
       </c>
       <c r="D37">
-        <v>1483.287161687984</v>
+        <v>1460.348680566617</v>
       </c>
       <c r="E37">
-        <v>121.9850000000001</v>
+        <v>151.0960000000001</v>
       </c>
       <c r="F37">
-        <v>1018.885</v>
+        <v>1047.996</v>
       </c>
       <c r="G37">
         <v>71.3</v>
@@ -4327,37 +4327,37 @@
         <v>112.5</v>
       </c>
       <c r="M37">
-        <v>204.592108</v>
+        <v>210.4375968</v>
       </c>
       <c r="N37">
-        <v>-92.09210800000005</v>
+        <v>-97.93759680000005</v>
       </c>
       <c r="O37">
-        <v>-22.10210592000001</v>
+        <v>-23.50502323200001</v>
       </c>
       <c r="P37">
-        <v>-69.99000208000004</v>
+        <v>-74.43257356800004</v>
       </c>
       <c r="Q37">
-        <v>151.90999792</v>
+        <v>147.467426432</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1043110370682371</v>
+        <v>0.1052252720224283</v>
       </c>
       <c r="T37">
-        <v>1.203048506056506</v>
+        <v>1.221846138963639</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.131969899836019</v>
+        <v>0.1283040692850185</v>
       </c>
       <c r="W37">
-        <v>0.1743004441129274</v>
+        <v>0.1750365428875683</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.5498745826500793</v>
+        <v>0.5346002886875771</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1303573295338787</v>
+        <v>0.1319073295338787</v>
       </c>
       <c r="C38">
-        <v>483.6526805666165</v>
+        <v>432.3018649057231</v>
       </c>
       <c r="D38">
-        <v>1460.348680566616</v>
+        <v>1438.108864905723</v>
       </c>
       <c r="E38">
-        <v>151.0959999999999</v>
+        <v>180.207</v>
       </c>
       <c r="F38">
-        <v>1047.996</v>
+        <v>1077.107</v>
       </c>
       <c r="G38">
         <v>71.3</v>
@@ -4409,37 +4409,37 @@
         <v>112.5</v>
       </c>
       <c r="M38">
-        <v>210.4375968</v>
+        <v>216.2830856</v>
       </c>
       <c r="N38">
-        <v>-97.93759679999999</v>
+        <v>-103.7830856</v>
       </c>
       <c r="O38">
-        <v>-23.505023232</v>
+        <v>-24.90794054400001</v>
       </c>
       <c r="P38">
-        <v>-74.432573568</v>
+        <v>-78.87514505600001</v>
       </c>
       <c r="Q38">
-        <v>147.467426432</v>
+        <v>143.024854944</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1052252720224283</v>
+        <v>0.1061685303084985</v>
       </c>
       <c r="T38">
-        <v>1.221846138963639</v>
+        <v>1.241240522121792</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.1283040692850185</v>
+        <v>0.1248363917367748</v>
       </c>
       <c r="W38">
-        <v>0.1750365428875683</v>
+        <v>0.1757328525392556</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.5346002886875774</v>
+        <v>0.5201516322365616</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1319073295338787</v>
+        <v>0.1334573295338786</v>
       </c>
       <c r="C39">
-        <v>432.3018649057231</v>
+        <v>381.6182733624989</v>
       </c>
       <c r="D39">
-        <v>1438.108864905723</v>
+        <v>1416.536273362499</v>
       </c>
       <c r="E39">
-        <v>180.207</v>
+        <v>209.3180000000001</v>
       </c>
       <c r="F39">
-        <v>1077.107</v>
+        <v>1106.218</v>
       </c>
       <c r="G39">
         <v>71.3</v>
@@ -4491,37 +4491,37 @@
         <v>112.5</v>
       </c>
       <c r="M39">
-        <v>216.2830856</v>
+        <v>222.1285744</v>
       </c>
       <c r="N39">
-        <v>-103.7830856</v>
+        <v>-109.6285744</v>
       </c>
       <c r="O39">
-        <v>-24.90794054400001</v>
+        <v>-26.31085785600001</v>
       </c>
       <c r="P39">
-        <v>-78.87514505600001</v>
+        <v>-83.31771654400004</v>
       </c>
       <c r="Q39">
-        <v>143.024854944</v>
+        <v>138.582283456</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1061685303084985</v>
+        <v>0.1071422162812163</v>
       </c>
       <c r="T39">
-        <v>1.241240522121792</v>
+        <v>1.261260530543111</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.1248363917367748</v>
+        <v>0.1215512235331754</v>
       </c>
       <c r="W39">
-        <v>0.1757328525392556</v>
+        <v>0.1763925143145384</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.5201516322365616</v>
+        <v>0.506463431388231</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1334573295338786</v>
+        <v>0.1489307029075586</v>
       </c>
       <c r="C40">
-        <v>381.6182733624989</v>
+        <v>168.0106031563469</v>
       </c>
       <c r="D40">
-        <v>1416.536273362499</v>
+        <v>1232.039603156347</v>
       </c>
       <c r="E40">
-        <v>209.3180000000001</v>
+        <v>238.429</v>
       </c>
       <c r="F40">
-        <v>1106.218</v>
+        <v>1135.329</v>
       </c>
       <c r="G40">
         <v>71.3</v>
@@ -4573,45 +4573,45 @@
         <v>112.5</v>
       </c>
       <c r="M40">
-        <v>222.1285744</v>
+        <v>267.7105782</v>
       </c>
       <c r="N40">
-        <v>-109.6285744</v>
+        <v>-155.2105782</v>
       </c>
       <c r="O40">
-        <v>-26.31085785600001</v>
+        <v>-37.25053876800001</v>
       </c>
       <c r="P40">
-        <v>-83.31771654400004</v>
+        <v>-117.960039432</v>
       </c>
       <c r="Q40">
-        <v>138.582283456</v>
+        <v>103.939960568</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1071422162812163</v>
+        <v>0.1085959794557935</v>
       </c>
       <c r="T40">
-        <v>1.261260530543111</v>
+        <v>1.291151431524671</v>
       </c>
       <c r="U40">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.1215512235331754</v>
+        <v>0.1008551854078361</v>
       </c>
       <c r="W40">
-        <v>0.1763925143145384</v>
+        <v>0.2120183472808322</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y40">
-        <v>0.506463431388231</v>
+        <v>0.4202299391993169</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1489307029075586</v>
+        <v>0.1508307029075586</v>
       </c>
       <c r="C41">
-        <v>168.0106031563469</v>
+        <v>119.5057819009498</v>
       </c>
       <c r="D41">
-        <v>1232.039603156347</v>
+        <v>1212.64578190095</v>
       </c>
       <c r="E41">
-        <v>238.429</v>
+        <v>267.5400000000001</v>
       </c>
       <c r="F41">
-        <v>1135.329</v>
+        <v>1164.44</v>
       </c>
       <c r="G41">
         <v>71.3</v>
@@ -4655,37 +4655,37 @@
         <v>112.5</v>
       </c>
       <c r="M41">
-        <v>267.7105782</v>
+        <v>274.574952</v>
       </c>
       <c r="N41">
-        <v>-155.2105782</v>
+        <v>-162.074952</v>
       </c>
       <c r="O41">
-        <v>-37.25053876800001</v>
+        <v>-38.89798848</v>
       </c>
       <c r="P41">
-        <v>-117.960039432</v>
+        <v>-123.17696352</v>
       </c>
       <c r="Q41">
-        <v>103.939960568</v>
+        <v>98.72303647999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1085959794557935</v>
+        <v>0.10964257911339</v>
       </c>
       <c r="T41">
-        <v>1.291151431524671</v>
+        <v>1.312670622050083</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.1008551854078361</v>
+        <v>0.09833380577264014</v>
       </c>
       <c r="W41">
-        <v>0.2120183472808322</v>
+        <v>0.2126128885988114</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.4202299391993169</v>
+        <v>0.409724190719334</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1508307029075586</v>
+        <v>0.1527307029075586</v>
       </c>
       <c r="C42">
-        <v>119.5057819009498</v>
+        <v>71.60206382139745</v>
       </c>
       <c r="D42">
-        <v>1212.64578190095</v>
+        <v>1193.853063821398</v>
       </c>
       <c r="E42">
-        <v>267.5400000000001</v>
+        <v>296.6510000000002</v>
       </c>
       <c r="F42">
-        <v>1164.44</v>
+        <v>1193.551</v>
       </c>
       <c r="G42">
         <v>71.3</v>
@@ -4737,37 +4737,37 @@
         <v>112.5</v>
       </c>
       <c r="M42">
-        <v>274.574952</v>
+        <v>281.4393258000001</v>
       </c>
       <c r="N42">
-        <v>-162.074952</v>
+        <v>-168.9393258000001</v>
       </c>
       <c r="O42">
-        <v>-38.89798848</v>
+        <v>-40.54543819200002</v>
       </c>
       <c r="P42">
-        <v>-123.17696352</v>
+        <v>-128.3938876080001</v>
       </c>
       <c r="Q42">
-        <v>98.72303647999999</v>
+        <v>93.50611239199995</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.10964257911339</v>
+        <v>0.1107246567254814</v>
       </c>
       <c r="T42">
-        <v>1.312670622050083</v>
+        <v>1.334919276661101</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.09833380577264014</v>
+        <v>0.09593542026599038</v>
       </c>
       <c r="W42">
-        <v>0.2126128885988114</v>
+        <v>0.2131784279012795</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.409724190719334</v>
+        <v>0.3997309177749598</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1527307029075586</v>
+        <v>0.1546307029075586</v>
       </c>
       <c r="C43">
-        <v>71.60206382139745</v>
+        <v>24.27192899886268</v>
       </c>
       <c r="D43">
-        <v>1193.853063821398</v>
+        <v>1175.633928998863</v>
       </c>
       <c r="E43">
-        <v>296.6510000000002</v>
+        <v>325.7620000000001</v>
       </c>
       <c r="F43">
-        <v>1193.551</v>
+        <v>1222.662</v>
       </c>
       <c r="G43">
         <v>71.3</v>
@@ -4819,37 +4819,37 @@
         <v>112.5</v>
       </c>
       <c r="M43">
-        <v>281.4393258000001</v>
+        <v>288.3036996</v>
       </c>
       <c r="N43">
-        <v>-168.9393258000001</v>
+        <v>-175.8036996</v>
       </c>
       <c r="O43">
-        <v>-40.54543819200002</v>
+        <v>-42.19288790400001</v>
       </c>
       <c r="P43">
-        <v>-128.3938876080001</v>
+        <v>-133.610811696</v>
       </c>
       <c r="Q43">
-        <v>93.50611239199995</v>
+        <v>88.28918830399996</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1107246567254814</v>
+        <v>0.1118440473586793</v>
       </c>
       <c r="T43">
-        <v>1.334919276661101</v>
+        <v>1.357935126258706</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.09593542026599038</v>
+        <v>0.09365124359299062</v>
       </c>
       <c r="W43">
-        <v>0.2131784279012795</v>
+        <v>0.2137170367607728</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3997309177749598</v>
+        <v>0.3902135149707943</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1546307029075586</v>
+        <v>0.1565307029075586</v>
       </c>
       <c r="C44">
-        <v>24.27192899886268</v>
+        <v>-22.51048783450779</v>
       </c>
       <c r="D44">
-        <v>1175.633928998863</v>
+        <v>1157.962512165492</v>
       </c>
       <c r="E44">
-        <v>325.7619999999998</v>
+        <v>354.8729999999999</v>
       </c>
       <c r="F44">
-        <v>1222.662</v>
+        <v>1251.773</v>
       </c>
       <c r="G44">
         <v>71.3</v>
@@ -4901,37 +4901,37 @@
         <v>112.5</v>
       </c>
       <c r="M44">
-        <v>288.3036996</v>
+        <v>295.1680734</v>
       </c>
       <c r="N44">
-        <v>-175.8036996</v>
+        <v>-182.6680734</v>
       </c>
       <c r="O44">
-        <v>-42.192887904</v>
+        <v>-43.840337616</v>
       </c>
       <c r="P44">
-        <v>-133.610811696</v>
+        <v>-138.827735784</v>
       </c>
       <c r="Q44">
-        <v>88.28918830400002</v>
+        <v>83.07226421600001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1118440473586793</v>
+        <v>0.1130027148562</v>
       </c>
       <c r="T44">
-        <v>1.357935126258706</v>
+        <v>1.381758549526403</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.09365124359299064</v>
+        <v>0.09147330769547922</v>
       </c>
       <c r="W44">
-        <v>0.2137170367607728</v>
+        <v>0.214230594045406</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3902135149707943</v>
+        <v>0.3811387820644968</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1565307029075586</v>
+        <v>0.1584307029075586</v>
       </c>
       <c r="C45">
-        <v>-22.51048783450779</v>
+        <v>-68.76951981254479</v>
       </c>
       <c r="D45">
-        <v>1157.962512165492</v>
+        <v>1140.814480187455</v>
       </c>
       <c r="E45">
-        <v>354.8729999999999</v>
+        <v>383.984</v>
       </c>
       <c r="F45">
-        <v>1251.773</v>
+        <v>1280.884</v>
       </c>
       <c r="G45">
         <v>71.3</v>
@@ -4983,37 +4983,37 @@
         <v>112.5</v>
       </c>
       <c r="M45">
-        <v>295.1680734</v>
+        <v>302.0324472</v>
       </c>
       <c r="N45">
-        <v>-182.6680734</v>
+        <v>-189.5324472000001</v>
       </c>
       <c r="O45">
-        <v>-43.840337616</v>
+        <v>-45.48778732800001</v>
       </c>
       <c r="P45">
-        <v>-138.827735784</v>
+        <v>-144.0446598720001</v>
       </c>
       <c r="Q45">
-        <v>83.07226421600001</v>
+        <v>77.85534012799994</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1130027148562</v>
+        <v>0.114202763335775</v>
       </c>
       <c r="T45">
-        <v>1.381758549526403</v>
+        <v>1.406432809339374</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.09147330769547922</v>
+        <v>0.0893943688842183</v>
       </c>
       <c r="W45">
-        <v>0.214230594045406</v>
+        <v>0.2147208078171013</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3811387820644968</v>
+        <v>0.3724765370175763</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1584307029075586</v>
+        <v>0.1603307029075586</v>
       </c>
       <c r="C46">
-        <v>-68.76951981254479</v>
+        <v>-114.5280797248929</v>
       </c>
       <c r="D46">
-        <v>1140.814480187455</v>
+        <v>1124.166920275107</v>
       </c>
       <c r="E46">
-        <v>383.984</v>
+        <v>413.0949999999999</v>
       </c>
       <c r="F46">
-        <v>1280.884</v>
+        <v>1309.995</v>
       </c>
       <c r="G46">
         <v>71.3</v>
@@ -5065,37 +5065,37 @@
         <v>112.5</v>
       </c>
       <c r="M46">
-        <v>302.0324472</v>
+        <v>308.896821</v>
       </c>
       <c r="N46">
-        <v>-189.5324472000001</v>
+        <v>-196.396821</v>
       </c>
       <c r="O46">
-        <v>-45.48778732800001</v>
+        <v>-47.13523704</v>
       </c>
       <c r="P46">
-        <v>-144.0446598720001</v>
+        <v>-149.26158396</v>
       </c>
       <c r="Q46">
-        <v>77.85534012799994</v>
+        <v>72.63841603999998</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.114202763335775</v>
+        <v>0.11544644994188</v>
       </c>
       <c r="T46">
-        <v>1.406432809339374</v>
+        <v>1.432004314963726</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.0893943688842183</v>
+        <v>0.08740782735345791</v>
       </c>
       <c r="W46">
-        <v>0.2147208078171013</v>
+        <v>0.2151892343100547</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3724765370175763</v>
+        <v>0.364199280639408</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1603307029075586</v>
+        <v>0.1622307029075586</v>
       </c>
       <c r="C47">
-        <v>-114.5280797248929</v>
+        <v>-159.8077621597365</v>
       </c>
       <c r="D47">
-        <v>1124.166920275107</v>
+        <v>1107.998237840264</v>
       </c>
       <c r="E47">
-        <v>413.0949999999999</v>
+        <v>442.206</v>
       </c>
       <c r="F47">
-        <v>1309.995</v>
+        <v>1339.106</v>
       </c>
       <c r="G47">
         <v>71.3</v>
@@ -5147,37 +5147,37 @@
         <v>112.5</v>
       </c>
       <c r="M47">
-        <v>308.896821</v>
+        <v>315.7611948</v>
       </c>
       <c r="N47">
-        <v>-196.396821</v>
+        <v>-203.2611948</v>
       </c>
       <c r="O47">
-        <v>-47.13523704</v>
+        <v>-48.782686752</v>
       </c>
       <c r="P47">
-        <v>-149.26158396</v>
+        <v>-154.478508048</v>
       </c>
       <c r="Q47">
-        <v>72.63841603999998</v>
+        <v>67.42149195199997</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.11544644994188</v>
+        <v>0.1167361990148778</v>
       </c>
       <c r="T47">
-        <v>1.432004314963726</v>
+        <v>1.458522913388981</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.08740782735345791</v>
+        <v>0.08550765719360014</v>
       </c>
       <c r="W47">
-        <v>0.2151892343100547</v>
+        <v>0.2156372944337491</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.364199280639408</v>
+        <v>0.3562819049733339</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1622307029075586</v>
+        <v>0.1641307029075586</v>
       </c>
       <c r="C48">
-        <v>-159.8077621597365</v>
+        <v>-204.6289369569033</v>
       </c>
       <c r="D48">
-        <v>1107.998237840264</v>
+        <v>1092.288063043097</v>
       </c>
       <c r="E48">
-        <v>442.206</v>
+        <v>471.3170000000001</v>
       </c>
       <c r="F48">
-        <v>1339.106</v>
+        <v>1368.217</v>
       </c>
       <c r="G48">
         <v>71.3</v>
@@ -5229,37 +5229,37 @@
         <v>112.5</v>
       </c>
       <c r="M48">
-        <v>315.7611948</v>
+        <v>322.6255686</v>
       </c>
       <c r="N48">
-        <v>-203.2611948</v>
+        <v>-210.1255686</v>
       </c>
       <c r="O48">
-        <v>-48.782686752</v>
+        <v>-50.43013646400001</v>
       </c>
       <c r="P48">
-        <v>-154.478508048</v>
+        <v>-159.695432136</v>
       </c>
       <c r="Q48">
-        <v>67.42149195199997</v>
+        <v>62.20456786399998</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1167361990148778</v>
+        <v>0.1180746178642151</v>
       </c>
       <c r="T48">
-        <v>1.458522913388981</v>
+        <v>1.486042213641603</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.08550765719360014</v>
+        <v>0.08368834533841714</v>
       </c>
       <c r="W48">
-        <v>0.2156372944337491</v>
+        <v>0.2160662881692012</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3562819049733339</v>
+        <v>0.3487014389100714</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1641307029075586</v>
+        <v>0.1660307029075586</v>
       </c>
       <c r="C49">
-        <v>-204.6289369569033</v>
+        <v>-249.0108348217595</v>
       </c>
       <c r="D49">
-        <v>1092.288063043097</v>
+        <v>1077.01716517824</v>
       </c>
       <c r="E49">
-        <v>471.3170000000001</v>
+        <v>500.428</v>
       </c>
       <c r="F49">
-        <v>1368.217</v>
+        <v>1397.328</v>
       </c>
       <c r="G49">
         <v>71.3</v>
@@ -5311,37 +5311,37 @@
         <v>112.5</v>
       </c>
       <c r="M49">
-        <v>322.6255686</v>
+        <v>329.4899424</v>
       </c>
       <c r="N49">
-        <v>-210.1255686</v>
+        <v>-216.9899424</v>
       </c>
       <c r="O49">
-        <v>-50.43013646400001</v>
+        <v>-52.07758617600001</v>
       </c>
       <c r="P49">
-        <v>-159.695432136</v>
+        <v>-164.912356224</v>
       </c>
       <c r="Q49">
-        <v>62.20456786399998</v>
+        <v>56.98764377599997</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1180746178642151</v>
+        <v>0.1194645143616039</v>
       </c>
       <c r="T49">
-        <v>1.486042213641603</v>
+        <v>1.514619948519326</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.08368834533841714</v>
+        <v>0.08194483814386679</v>
       </c>
       <c r="W49">
-        <v>0.2160662881692012</v>
+        <v>0.2164774071656762</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3487014389100714</v>
+        <v>0.341436825599445</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1660307029075586</v>
+        <v>0.1679307029075586</v>
       </c>
       <c r="C50">
-        <v>-249.0108348217595</v>
+        <v>-292.9716258564965</v>
       </c>
       <c r="D50">
-        <v>1077.01716517824</v>
+        <v>1062.167374143503</v>
       </c>
       <c r="E50">
-        <v>500.428</v>
+        <v>529.5389999999999</v>
       </c>
       <c r="F50">
-        <v>1397.328</v>
+        <v>1426.439</v>
       </c>
       <c r="G50">
         <v>71.3</v>
@@ -5393,37 +5393,37 @@
         <v>112.5</v>
       </c>
       <c r="M50">
-        <v>329.4899424</v>
+        <v>336.3543162</v>
       </c>
       <c r="N50">
-        <v>-216.9899424</v>
+        <v>-223.8543162</v>
       </c>
       <c r="O50">
-        <v>-52.07758617600001</v>
+        <v>-53.725035888</v>
       </c>
       <c r="P50">
-        <v>-164.912356224</v>
+        <v>-170.129280312</v>
       </c>
       <c r="Q50">
-        <v>56.98764377599997</v>
+        <v>51.77071968800001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1194645143616039</v>
+        <v>0.1209089166039883</v>
       </c>
       <c r="T50">
-        <v>1.514619948519326</v>
+        <v>1.54431837888245</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.08194483814386679</v>
+        <v>0.08027249450827767</v>
       </c>
       <c r="W50">
-        <v>0.2164774071656762</v>
+        <v>0.2168717457949481</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.341436825599445</v>
+        <v>0.3344687271178237</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1679307029075586</v>
+        <v>0.1698307029075586</v>
       </c>
       <c r="C51">
-        <v>-292.9716258564965</v>
+        <v>-336.5284916830922</v>
       </c>
       <c r="D51">
-        <v>1062.167374143503</v>
+        <v>1047.721508316908</v>
       </c>
       <c r="E51">
-        <v>529.5389999999999</v>
+        <v>558.65</v>
       </c>
       <c r="F51">
-        <v>1426.439</v>
+        <v>1455.55</v>
       </c>
       <c r="G51">
         <v>71.3</v>
@@ -5475,37 +5475,37 @@
         <v>112.5</v>
       </c>
       <c r="M51">
-        <v>336.3543162</v>
+        <v>343.21869</v>
       </c>
       <c r="N51">
-        <v>-223.8543162</v>
+        <v>-230.71869</v>
       </c>
       <c r="O51">
-        <v>-53.725035888</v>
+        <v>-55.3724856</v>
       </c>
       <c r="P51">
-        <v>-170.129280312</v>
+        <v>-175.3462044</v>
       </c>
       <c r="Q51">
-        <v>51.77071968800001</v>
+        <v>46.5537956</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1209089166039883</v>
+        <v>0.122411094936068</v>
       </c>
       <c r="T51">
-        <v>1.54431837888245</v>
+        <v>1.575204746460099</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.08027249450827767</v>
+        <v>0.07866704461811212</v>
       </c>
       <c r="W51">
-        <v>0.2168717457949481</v>
+        <v>0.2172503108790492</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3344687271178237</v>
+        <v>0.3277793525754672</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1698307029075586</v>
+        <v>0.1717307029075586</v>
       </c>
       <c r="C52">
-        <v>-336.5284916830922</v>
+        <v>-379.697691759849</v>
       </c>
       <c r="D52">
-        <v>1047.721508316908</v>
+        <v>1033.663308240151</v>
       </c>
       <c r="E52">
-        <v>558.65</v>
+        <v>587.7610000000001</v>
       </c>
       <c r="F52">
-        <v>1455.55</v>
+        <v>1484.661</v>
       </c>
       <c r="G52">
         <v>71.3</v>
@@ -5557,37 +5557,37 @@
         <v>112.5</v>
       </c>
       <c r="M52">
-        <v>343.21869</v>
+        <v>350.0830638</v>
       </c>
       <c r="N52">
-        <v>-230.71869</v>
+        <v>-237.5830638000001</v>
       </c>
       <c r="O52">
-        <v>-55.3724856</v>
+        <v>-57.01993531200002</v>
       </c>
       <c r="P52">
-        <v>-175.3462044</v>
+        <v>-180.5631284880001</v>
       </c>
       <c r="Q52">
-        <v>46.5537956</v>
+        <v>41.33687151199993</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.122411094936068</v>
+        <v>0.1239745866694572</v>
       </c>
       <c r="T52">
-        <v>1.575204746460099</v>
+        <v>1.607351782102142</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.07866704461811212</v>
+        <v>0.07712455354716873</v>
       </c>
       <c r="W52">
-        <v>0.2172503108790492</v>
+        <v>0.2176140302735776</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3277793525754672</v>
+        <v>0.3213523064465365</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1717307029075586</v>
+        <v>0.1736307029075586</v>
       </c>
       <c r="C53">
-        <v>-379.697691759849</v>
+        <v>-422.494624429655</v>
       </c>
       <c r="D53">
-        <v>1033.663308240151</v>
+        <v>1019.977375570345</v>
       </c>
       <c r="E53">
-        <v>587.7610000000001</v>
+        <v>616.872</v>
       </c>
       <c r="F53">
-        <v>1484.661</v>
+        <v>1513.772</v>
       </c>
       <c r="G53">
         <v>71.3</v>
@@ -5639,37 +5639,37 @@
         <v>112.5</v>
       </c>
       <c r="M53">
-        <v>350.0830638</v>
+        <v>356.9474376</v>
       </c>
       <c r="N53">
-        <v>-237.5830638000001</v>
+        <v>-244.4474376</v>
       </c>
       <c r="O53">
-        <v>-57.01993531200002</v>
+        <v>-58.667385024</v>
       </c>
       <c r="P53">
-        <v>-180.5631284880001</v>
+        <v>-185.780052576</v>
       </c>
       <c r="Q53">
-        <v>41.33687151199993</v>
+        <v>36.11994742399997</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1239745866694572</v>
+        <v>0.1256032238917375</v>
       </c>
       <c r="T53">
-        <v>1.607351782102142</v>
+        <v>1.640838277562603</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.07712455354716873</v>
+        <v>0.07564138905587703</v>
       </c>
       <c r="W53">
-        <v>0.2176140302735776</v>
+        <v>0.2179637604606242</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3213523064465365</v>
+        <v>0.3151724543994877</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1736307029075586</v>
+        <v>0.1755307029075586</v>
       </c>
       <c r="C54">
-        <v>-422.494624429655</v>
+        <v>-464.9338831818677</v>
       </c>
       <c r="D54">
-        <v>1019.977375570345</v>
+        <v>1006.649116818132</v>
       </c>
       <c r="E54">
-        <v>616.872</v>
+        <v>645.9830000000001</v>
       </c>
       <c r="F54">
-        <v>1513.772</v>
+        <v>1542.883</v>
       </c>
       <c r="G54">
         <v>71.3</v>
@@ -5721,37 +5721,37 @@
         <v>112.5</v>
       </c>
       <c r="M54">
-        <v>356.9474376</v>
+        <v>363.8118114</v>
       </c>
       <c r="N54">
-        <v>-244.4474376</v>
+        <v>-251.3118114</v>
       </c>
       <c r="O54">
-        <v>-58.667385024</v>
+        <v>-60.31483473600001</v>
       </c>
       <c r="P54">
-        <v>-185.780052576</v>
+        <v>-190.996976664</v>
       </c>
       <c r="Q54">
-        <v>36.11994742399997</v>
+        <v>30.90302333599996</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1256032238917375</v>
+        <v>0.1273011648256043</v>
       </c>
       <c r="T54">
-        <v>1.640838277562603</v>
+        <v>1.675749730276701</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.07564138905587703</v>
+        <v>0.07421419303595482</v>
       </c>
       <c r="W54">
-        <v>0.2179637604606242</v>
+        <v>0.2183002932821219</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3151724543994877</v>
+        <v>0.3092258043164785</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1755307029075586</v>
+        <v>0.1774307029075586</v>
       </c>
       <c r="C55">
-        <v>-464.9338831818677</v>
+        <v>-507.0293085599742</v>
       </c>
       <c r="D55">
-        <v>1006.649116818132</v>
+        <v>993.6646914400259</v>
       </c>
       <c r="E55">
-        <v>645.9830000000001</v>
+        <v>675.0940000000002</v>
       </c>
       <c r="F55">
-        <v>1542.883</v>
+        <v>1571.994</v>
       </c>
       <c r="G55">
         <v>71.3</v>
@@ -5803,37 +5803,37 @@
         <v>112.5</v>
       </c>
       <c r="M55">
-        <v>363.8118114</v>
+        <v>370.6761852</v>
       </c>
       <c r="N55">
-        <v>-251.3118114</v>
+        <v>-258.1761852000001</v>
       </c>
       <c r="O55">
-        <v>-60.31483473600001</v>
+        <v>-61.96228444800002</v>
       </c>
       <c r="P55">
-        <v>-190.996976664</v>
+        <v>-196.2139007520001</v>
       </c>
       <c r="Q55">
-        <v>30.90302333599996</v>
+        <v>25.68609924799995</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1273011648256043</v>
+        <v>0.1290729292783348</v>
       </c>
       <c r="T55">
-        <v>1.675749730276701</v>
+        <v>1.712179072239238</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.07421419303595482</v>
+        <v>0.07283985612788159</v>
       </c>
       <c r="W55">
-        <v>0.2183002932821219</v>
+        <v>0.2186243619250455</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3092258043164785</v>
+        <v>0.3034994005328399</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1774307029075586</v>
+        <v>0.1793307029075586</v>
       </c>
       <c r="C56">
-        <v>-507.0293085599742</v>
+        <v>-548.7940361031776</v>
       </c>
       <c r="D56">
-        <v>993.6646914400259</v>
+        <v>981.0109638968224</v>
       </c>
       <c r="E56">
-        <v>675.0940000000002</v>
+        <v>704.205</v>
       </c>
       <c r="F56">
-        <v>1571.994</v>
+        <v>1601.105</v>
       </c>
       <c r="G56">
         <v>71.3</v>
@@ -5885,37 +5885,37 @@
         <v>112.5</v>
       </c>
       <c r="M56">
-        <v>370.6761852</v>
+        <v>377.540559</v>
       </c>
       <c r="N56">
-        <v>-258.1761852000001</v>
+        <v>-265.040559</v>
       </c>
       <c r="O56">
-        <v>-61.96228444800002</v>
+        <v>-63.60973416</v>
       </c>
       <c r="P56">
-        <v>-196.2139007520001</v>
+        <v>-201.43082484</v>
       </c>
       <c r="Q56">
-        <v>25.68609924799995</v>
+        <v>20.46917515999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1290729292783348</v>
+        <v>0.1309234388178534</v>
       </c>
       <c r="T56">
-        <v>1.712179072239238</v>
+        <v>1.750227496066777</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.07283985612788159</v>
+        <v>0.07151549510737465</v>
       </c>
       <c r="W56">
-        <v>0.2186243619250455</v>
+        <v>0.2189366462536811</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3034994005328399</v>
+        <v>0.2979812296140611</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1793307029075586</v>
+        <v>0.1812307029075586</v>
       </c>
       <c r="C57">
-        <v>-548.7940361031776</v>
+        <v>-590.2405406709938</v>
       </c>
       <c r="D57">
-        <v>981.0109638968224</v>
+        <v>968.6754593290062</v>
       </c>
       <c r="E57">
-        <v>704.205</v>
+        <v>733.3160000000001</v>
       </c>
       <c r="F57">
-        <v>1601.105</v>
+        <v>1630.216</v>
       </c>
       <c r="G57">
         <v>71.3</v>
@@ -5967,37 +5967,37 @@
         <v>112.5</v>
       </c>
       <c r="M57">
-        <v>377.540559</v>
+        <v>384.4049328</v>
       </c>
       <c r="N57">
-        <v>-265.040559</v>
+        <v>-271.9049328000001</v>
       </c>
       <c r="O57">
-        <v>-63.60973416</v>
+        <v>-65.25718387200003</v>
       </c>
       <c r="P57">
-        <v>-201.43082484</v>
+        <v>-206.6477489280001</v>
       </c>
       <c r="Q57">
-        <v>20.46917515999999</v>
+        <v>15.25225107199995</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1309234388178534</v>
+        <v>0.13285806242735</v>
       </c>
       <c r="T57">
-        <v>1.750227496066777</v>
+        <v>1.790005393704658</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.07151549510737465</v>
+        <v>0.07023843269474296</v>
       </c>
       <c r="W57">
-        <v>0.2189366462536811</v>
+        <v>0.2192377775705796</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2979812296140611</v>
+        <v>0.2926601362280956</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1812307029075586</v>
+        <v>0.1831307029075586</v>
       </c>
       <c r="C58">
-        <v>-590.2405406709938</v>
+        <v>-631.380677465283</v>
       </c>
       <c r="D58">
-        <v>968.6754593290062</v>
+        <v>956.6463225347172</v>
       </c>
       <c r="E58">
-        <v>733.3160000000001</v>
+        <v>762.4270000000002</v>
       </c>
       <c r="F58">
-        <v>1630.216</v>
+        <v>1659.327</v>
       </c>
       <c r="G58">
         <v>71.3</v>
@@ -6049,37 +6049,37 @@
         <v>112.5</v>
       </c>
       <c r="M58">
-        <v>384.4049328</v>
+        <v>391.2693066</v>
       </c>
       <c r="N58">
-        <v>-271.9049328000001</v>
+        <v>-278.7693066</v>
       </c>
       <c r="O58">
-        <v>-65.25718387200003</v>
+        <v>-66.90463358400001</v>
       </c>
       <c r="P58">
-        <v>-206.6477489280001</v>
+        <v>-211.864673016</v>
       </c>
       <c r="Q58">
-        <v>15.25225107199995</v>
+        <v>10.03532698399997</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.13285806242735</v>
+        <v>0.1348826685303117</v>
       </c>
       <c r="T58">
-        <v>1.790005393704658</v>
+        <v>1.831633426116394</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.07023843269474296</v>
+        <v>0.06900617948957202</v>
       </c>
       <c r="W58">
-        <v>0.2192377775705796</v>
+        <v>0.2195283428763589</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2926601362280956</v>
+        <v>0.2875257478732168</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1831307029075586</v>
+        <v>0.1850307029075586</v>
       </c>
       <c r="C59">
-        <v>-631.380677465283</v>
+        <v>-672.2257200332616</v>
       </c>
       <c r="D59">
-        <v>956.6463225347172</v>
+        <v>944.9122799667385</v>
       </c>
       <c r="E59">
-        <v>762.4270000000002</v>
+        <v>791.5380000000001</v>
       </c>
       <c r="F59">
-        <v>1659.327</v>
+        <v>1688.438</v>
       </c>
       <c r="G59">
         <v>71.3</v>
@@ -6131,37 +6131,37 @@
         <v>112.5</v>
       </c>
       <c r="M59">
-        <v>391.2693066</v>
+        <v>398.1336804000001</v>
       </c>
       <c r="N59">
-        <v>-278.7693066</v>
+        <v>-285.6336804000001</v>
       </c>
       <c r="O59">
-        <v>-66.90463358400001</v>
+        <v>-68.55208329600002</v>
       </c>
       <c r="P59">
-        <v>-211.864673016</v>
+        <v>-217.0815971040001</v>
       </c>
       <c r="Q59">
-        <v>10.03532698399997</v>
+        <v>4.818402895999924</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1348826685303117</v>
+        <v>0.1370036844477001</v>
       </c>
       <c r="T59">
-        <v>1.831633426116394</v>
+        <v>1.875243745785832</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.06900617948957202</v>
+        <v>0.06781641777423458</v>
       </c>
       <c r="W59">
-        <v>0.2195283428763589</v>
+        <v>0.2198088886888355</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2875257478732168</v>
+        <v>0.282568407392644</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1850307029075586</v>
+        <v>0.1869307029075586</v>
       </c>
       <c r="C60">
-        <v>-672.2257200332614</v>
+        <v>-712.7863955075878</v>
       </c>
       <c r="D60">
-        <v>944.9122799667385</v>
+        <v>933.462604492412</v>
       </c>
       <c r="E60">
-        <v>791.5379999999999</v>
+        <v>820.6489999999998</v>
       </c>
       <c r="F60">
-        <v>1688.438</v>
+        <v>1717.549</v>
       </c>
       <c r="G60">
         <v>71.3</v>
@@ -6213,37 +6213,37 @@
         <v>112.5</v>
       </c>
       <c r="M60">
-        <v>398.1336804</v>
+        <v>404.9980542</v>
       </c>
       <c r="N60">
-        <v>-285.6336804</v>
+        <v>-292.4980542</v>
       </c>
       <c r="O60">
-        <v>-68.55208329599999</v>
+        <v>-70.19953300799999</v>
       </c>
       <c r="P60">
-        <v>-217.081597104</v>
+        <v>-222.298521192</v>
       </c>
       <c r="Q60">
-        <v>4.818402895999981</v>
+        <v>-0.3985211919999472</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1370036844477</v>
+        <v>0.1392281645561805</v>
       </c>
       <c r="T60">
-        <v>1.875243745785832</v>
+        <v>1.920981398122072</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.06781641777423458</v>
+        <v>0.0666669869645018</v>
       </c>
       <c r="W60">
-        <v>0.2198088886888355</v>
+        <v>0.2200799244737705</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2825684073926442</v>
+        <v>0.277779112352091</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1869307029075586</v>
+        <v>0.1888307029075586</v>
       </c>
       <c r="C61">
-        <v>-712.7863955075878</v>
+        <v>-753.0729173150492</v>
       </c>
       <c r="D61">
-        <v>933.462604492412</v>
+        <v>922.2870826849507</v>
       </c>
       <c r="E61">
-        <v>820.6489999999998</v>
+        <v>849.7599999999999</v>
       </c>
       <c r="F61">
-        <v>1717.549</v>
+        <v>1746.66</v>
       </c>
       <c r="G61">
         <v>71.3</v>
@@ -6295,37 +6295,37 @@
         <v>112.5</v>
       </c>
       <c r="M61">
-        <v>404.9980542</v>
+        <v>411.862428</v>
       </c>
       <c r="N61">
-        <v>-292.4980542</v>
+        <v>-299.362428</v>
       </c>
       <c r="O61">
-        <v>-70.19953300799999</v>
+        <v>-71.84698272</v>
       </c>
       <c r="P61">
-        <v>-222.298521192</v>
+        <v>-227.51544528</v>
       </c>
       <c r="Q61">
-        <v>-0.3985211919999472</v>
+        <v>-5.615445280000017</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1392281645561805</v>
+        <v>0.1415638686700851</v>
       </c>
       <c r="T61">
-        <v>1.920981398122072</v>
+        <v>1.969005933075124</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.0666669869645018</v>
+        <v>0.06555587051509344</v>
       </c>
       <c r="W61">
-        <v>0.2200799244737705</v>
+        <v>0.220341925732541</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.277779112352091</v>
+        <v>0.2731494604795559</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1888307029075586</v>
+        <v>0.1907307029075586</v>
       </c>
       <c r="C62">
-        <v>-753.0729173150492</v>
+        <v>-793.0950155634946</v>
       </c>
       <c r="D62">
-        <v>922.2870826849507</v>
+        <v>911.3759844365054</v>
       </c>
       <c r="E62">
-        <v>849.7599999999999</v>
+        <v>878.871</v>
       </c>
       <c r="F62">
-        <v>1746.66</v>
+        <v>1775.771</v>
       </c>
       <c r="G62">
         <v>71.3</v>
@@ -6377,37 +6377,37 @@
         <v>112.5</v>
       </c>
       <c r="M62">
-        <v>411.862428</v>
+        <v>418.7268018</v>
       </c>
       <c r="N62">
-        <v>-299.362428</v>
+        <v>-306.2268018000001</v>
       </c>
       <c r="O62">
-        <v>-71.84698272</v>
+        <v>-73.49443243200002</v>
       </c>
       <c r="P62">
-        <v>-227.51544528</v>
+        <v>-232.7323693680001</v>
       </c>
       <c r="Q62">
-        <v>-5.615445280000017</v>
+        <v>-10.83236936800006</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1415638686700851</v>
+        <v>0.1440193524821385</v>
       </c>
       <c r="T62">
-        <v>1.969005933075124</v>
+        <v>2.019493264692434</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.06555587051509344</v>
+        <v>0.06448118411320666</v>
       </c>
       <c r="W62">
-        <v>0.220341925732541</v>
+        <v>0.2205953367861059</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2731494604795559</v>
+        <v>0.2686716004716944</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1907307029075586</v>
+        <v>0.1926307029075586</v>
       </c>
       <c r="C63">
-        <v>-793.0950155634946</v>
+        <v>-832.8619652970378</v>
       </c>
       <c r="D63">
-        <v>911.3759844365054</v>
+        <v>900.720034702962</v>
       </c>
       <c r="E63">
-        <v>878.871</v>
+        <v>907.9819999999999</v>
       </c>
       <c r="F63">
-        <v>1775.771</v>
+        <v>1804.882</v>
       </c>
       <c r="G63">
         <v>71.3</v>
@@ -6459,37 +6459,37 @@
         <v>112.5</v>
       </c>
       <c r="M63">
-        <v>418.7268018</v>
+        <v>425.5911756</v>
       </c>
       <c r="N63">
-        <v>-306.2268018000001</v>
+        <v>-313.0911756</v>
       </c>
       <c r="O63">
-        <v>-73.49443243200002</v>
+        <v>-75.14188214400001</v>
       </c>
       <c r="P63">
-        <v>-232.7323693680001</v>
+        <v>-237.949293456</v>
       </c>
       <c r="Q63">
-        <v>-10.83236936800006</v>
+        <v>-16.04929345600002</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1440193524821385</v>
+        <v>0.1466040722843001</v>
       </c>
       <c r="T63">
-        <v>2.019493264692434</v>
+        <v>2.072637824289604</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.06448118411320666</v>
+        <v>0.06344116501460655</v>
       </c>
       <c r="W63">
-        <v>0.2205953367861059</v>
+        <v>0.2208405732895558</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2686716004716944</v>
+        <v>0.2643381875608606</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1926307029075586</v>
+        <v>0.1945307029075586</v>
       </c>
       <c r="C64">
-        <v>-832.8619652970378</v>
+        <v>-872.3826127919807</v>
       </c>
       <c r="D64">
-        <v>900.720034702962</v>
+        <v>890.3103872080193</v>
       </c>
       <c r="E64">
-        <v>907.9819999999999</v>
+        <v>937.093</v>
       </c>
       <c r="F64">
-        <v>1804.882</v>
+        <v>1833.993</v>
       </c>
       <c r="G64">
         <v>71.3</v>
@@ -6541,37 +6541,37 @@
         <v>112.5</v>
       </c>
       <c r="M64">
-        <v>425.5911756</v>
+        <v>432.4555494</v>
       </c>
       <c r="N64">
-        <v>-313.0911756</v>
+        <v>-319.9555494</v>
       </c>
       <c r="O64">
-        <v>-75.14188214400001</v>
+        <v>-76.78933185599999</v>
       </c>
       <c r="P64">
-        <v>-237.949293456</v>
+        <v>-243.166217544</v>
       </c>
       <c r="Q64">
-        <v>-16.04929345600002</v>
+        <v>-21.266217544</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1466040722843001</v>
+        <v>0.1493285066703622</v>
       </c>
       <c r="T64">
-        <v>2.072637824289604</v>
+        <v>2.128655062783917</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.06344116501460655</v>
+        <v>0.06243416239532708</v>
       </c>
       <c r="W64">
-        <v>0.2208405732895558</v>
+        <v>0.2210780245071819</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2643381875608606</v>
+        <v>0.2601423433138629</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1945307029075586</v>
+        <v>0.1964307029075586</v>
       </c>
       <c r="C65">
-        <v>-872.3826127919807</v>
+        <v>-911.6654000501505</v>
       </c>
       <c r="D65">
-        <v>890.3103872080193</v>
+        <v>880.1385999498495</v>
       </c>
       <c r="E65">
-        <v>937.093</v>
+        <v>966.2040000000001</v>
       </c>
       <c r="F65">
-        <v>1833.993</v>
+        <v>1863.104</v>
       </c>
       <c r="G65">
         <v>71.3</v>
@@ -6623,37 +6623,37 @@
         <v>112.5</v>
       </c>
       <c r="M65">
-        <v>432.4555494</v>
+        <v>439.3199232</v>
       </c>
       <c r="N65">
-        <v>-319.9555494</v>
+        <v>-326.8199232000001</v>
       </c>
       <c r="O65">
-        <v>-76.78933185599999</v>
+        <v>-78.43678156800001</v>
       </c>
       <c r="P65">
-        <v>-243.166217544</v>
+        <v>-248.383141632</v>
       </c>
       <c r="Q65">
-        <v>-21.266217544</v>
+        <v>-26.48314163200004</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1493285066703622</v>
+        <v>0.1522042985223167</v>
       </c>
       <c r="T65">
-        <v>2.128655062783917</v>
+        <v>2.187784370083471</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.06243416239532708</v>
+        <v>0.06145862860790009</v>
       </c>
       <c r="W65">
-        <v>0.2210780245071819</v>
+        <v>0.2213080553742572</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2601423433138629</v>
+        <v>0.2560776191995837</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1964307029075586</v>
+        <v>0.1983307029075586</v>
       </c>
       <c r="C66">
-        <v>-911.6654000501505</v>
+        <v>-950.7183876321932</v>
       </c>
       <c r="D66">
-        <v>880.1385999498495</v>
+        <v>870.1966123678068</v>
       </c>
       <c r="E66">
-        <v>966.2040000000001</v>
+        <v>995.3149999999999</v>
       </c>
       <c r="F66">
-        <v>1863.104</v>
+        <v>1892.215</v>
       </c>
       <c r="G66">
         <v>71.3</v>
@@ -6705,37 +6705,37 @@
         <v>112.5</v>
       </c>
       <c r="M66">
-        <v>439.3199232</v>
+        <v>446.184297</v>
       </c>
       <c r="N66">
-        <v>-326.8199232000001</v>
+        <v>-333.684297</v>
       </c>
       <c r="O66">
-        <v>-78.43678156800001</v>
+        <v>-80.08423128</v>
       </c>
       <c r="P66">
-        <v>-248.383141632</v>
+        <v>-253.60006572</v>
       </c>
       <c r="Q66">
-        <v>-26.48314163200004</v>
+        <v>-31.70006572000003</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1522042985223167</v>
+        <v>0.1552444213372401</v>
       </c>
       <c r="T66">
-        <v>2.187784370083471</v>
+        <v>2.250292494942999</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.06145862860790009</v>
+        <v>0.06051311124470163</v>
       </c>
       <c r="W66">
-        <v>0.2213080553742572</v>
+        <v>0.2215310083684994</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2560776191995837</v>
+        <v>0.2521379635195902</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1983307029075586</v>
+        <v>0.2002307029075586</v>
       </c>
       <c r="C67">
-        <v>-950.7183876321932</v>
+        <v>-989.5492759606042</v>
       </c>
       <c r="D67">
-        <v>870.1966123678068</v>
+        <v>860.4767240393959</v>
       </c>
       <c r="E67">
-        <v>995.3149999999999</v>
+        <v>1024.426</v>
       </c>
       <c r="F67">
-        <v>1892.215</v>
+        <v>1921.326</v>
       </c>
       <c r="G67">
         <v>71.3</v>
@@ -6787,37 +6787,37 @@
         <v>112.5</v>
       </c>
       <c r="M67">
-        <v>446.184297</v>
+        <v>453.0486708</v>
       </c>
       <c r="N67">
-        <v>-333.684297</v>
+        <v>-340.5486708000001</v>
       </c>
       <c r="O67">
-        <v>-80.08423128</v>
+        <v>-81.73168099200002</v>
       </c>
       <c r="P67">
-        <v>-253.60006572</v>
+        <v>-258.8169898080001</v>
       </c>
       <c r="Q67">
-        <v>-31.70006572000003</v>
+        <v>-36.91698980800007</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1552444213372401</v>
+        <v>0.1584633749059824</v>
       </c>
       <c r="T67">
-        <v>2.250292494942999</v>
+        <v>2.316477568323675</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.06051311124470163</v>
+        <v>0.05959624592281221</v>
       </c>
       <c r="W67">
-        <v>0.2215310083684994</v>
+        <v>0.2217472052114009</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2521379635195902</v>
+        <v>0.2483176913450508</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2002307029075586</v>
+        <v>0.2021307029075586</v>
       </c>
       <c r="C68">
-        <v>-989.5492759606042</v>
+        <v>-1028.165425210837</v>
       </c>
       <c r="D68">
-        <v>860.4767240393959</v>
+        <v>850.9715747891635</v>
       </c>
       <c r="E68">
-        <v>1024.426</v>
+        <v>1053.537</v>
       </c>
       <c r="F68">
-        <v>1921.326</v>
+        <v>1950.437</v>
       </c>
       <c r="G68">
         <v>71.3</v>
@@ -6869,37 +6869,37 @@
         <v>112.5</v>
       </c>
       <c r="M68">
-        <v>453.0486708</v>
+        <v>459.9130446</v>
       </c>
       <c r="N68">
-        <v>-340.5486708000001</v>
+        <v>-347.4130446</v>
       </c>
       <c r="O68">
-        <v>-81.73168099200002</v>
+        <v>-83.379130704</v>
       </c>
       <c r="P68">
-        <v>-258.8169898080001</v>
+        <v>-264.0339138960001</v>
       </c>
       <c r="Q68">
-        <v>-36.91698980800007</v>
+        <v>-42.13391389600005</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1584633749059824</v>
+        <v>0.1618774165698001</v>
       </c>
       <c r="T68">
-        <v>2.316477568323675</v>
+        <v>2.386673858272878</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.05959624592281221</v>
+        <v>0.05870674971500904</v>
       </c>
       <c r="W68">
-        <v>0.2217472052114009</v>
+        <v>0.2219569484172009</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2483176913450508</v>
+        <v>0.2446114571458711</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2021307029075586</v>
+        <v>0.2040307029075586</v>
       </c>
       <c r="C69">
-        <v>-1028.165425210837</v>
+        <v>-1066.573873898464</v>
       </c>
       <c r="D69">
-        <v>850.9715747891635</v>
+        <v>841.6741261015362</v>
       </c>
       <c r="E69">
-        <v>1053.537</v>
+        <v>1082.648</v>
       </c>
       <c r="F69">
-        <v>1950.437</v>
+        <v>1979.548</v>
       </c>
       <c r="G69">
         <v>71.3</v>
@@ -6951,37 +6951,37 @@
         <v>112.5</v>
       </c>
       <c r="M69">
-        <v>459.9130446</v>
+        <v>466.7774184</v>
       </c>
       <c r="N69">
-        <v>-347.4130446</v>
+        <v>-354.2774184000001</v>
       </c>
       <c r="O69">
-        <v>-83.379130704</v>
+        <v>-85.02658041600002</v>
       </c>
       <c r="P69">
-        <v>-264.0339138960001</v>
+        <v>-269.2508379840001</v>
       </c>
       <c r="Q69">
-        <v>-42.13391389600005</v>
+        <v>-47.35083798400009</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1618774165698001</v>
+        <v>0.1655048358376063</v>
       </c>
       <c r="T69">
-        <v>2.386673858272878</v>
+        <v>2.461257416343905</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.05870674971500904</v>
+        <v>0.05784341516037655</v>
       </c>
       <c r="W69">
-        <v>0.2219569484172009</v>
+        <v>0.2221605227051832</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2446114571458711</v>
+        <v>0.2410142298349023</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2040307029075586</v>
+        <v>0.2059307029075586</v>
       </c>
       <c r="C70">
-        <v>-1066.573873898464</v>
+        <v>-1104.781356261046</v>
       </c>
       <c r="D70">
-        <v>841.6741261015362</v>
+        <v>832.5776437389538</v>
       </c>
       <c r="E70">
-        <v>1082.648</v>
+        <v>1111.759</v>
       </c>
       <c r="F70">
-        <v>1979.548</v>
+        <v>2008.659</v>
       </c>
       <c r="G70">
         <v>71.3</v>
@@ -7033,37 +7033,37 @@
         <v>112.5</v>
       </c>
       <c r="M70">
-        <v>466.7774184</v>
+        <v>473.6417922000001</v>
       </c>
       <c r="N70">
-        <v>-354.2774184000001</v>
+        <v>-361.1417922000001</v>
       </c>
       <c r="O70">
-        <v>-85.02658041600002</v>
+        <v>-86.67403012800001</v>
       </c>
       <c r="P70">
-        <v>-269.2508379840001</v>
+        <v>-274.467762072</v>
       </c>
       <c r="Q70">
-        <v>-47.35083798400009</v>
+        <v>-52.56776207200002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1655048358376063</v>
+        <v>0.1693662821549485</v>
       </c>
       <c r="T70">
-        <v>2.461257416343905</v>
+        <v>2.540652816871128</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.05784341516037655</v>
+        <v>0.05700510479573341</v>
       </c>
       <c r="W70">
-        <v>0.2221605227051832</v>
+        <v>0.2223581962891661</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2410142298349023</v>
+        <v>0.2375212699822227</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2059307029075586</v>
+        <v>0.2078307029075586</v>
       </c>
       <c r="C71">
-        <v>-1104.781356261046</v>
+        <v>-1142.79431852491</v>
       </c>
       <c r="D71">
-        <v>832.5776437389538</v>
+        <v>823.6756814750902</v>
       </c>
       <c r="E71">
-        <v>1111.759</v>
+        <v>1140.87</v>
       </c>
       <c r="F71">
-        <v>2008.659</v>
+        <v>2037.77</v>
       </c>
       <c r="G71">
         <v>71.3</v>
@@ -7115,37 +7115,37 @@
         <v>112.5</v>
       </c>
       <c r="M71">
-        <v>473.6417922000001</v>
+        <v>480.5061660000001</v>
       </c>
       <c r="N71">
-        <v>-361.1417922000001</v>
+        <v>-368.0061660000001</v>
       </c>
       <c r="O71">
-        <v>-86.67403012800001</v>
+        <v>-88.32147984000002</v>
       </c>
       <c r="P71">
-        <v>-274.467762072</v>
+        <v>-279.6846861600001</v>
       </c>
       <c r="Q71">
-        <v>-52.56776207200002</v>
+        <v>-57.78468616000006</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1693662821549485</v>
+        <v>0.1734851582267801</v>
       </c>
       <c r="T71">
-        <v>2.540652816871128</v>
+        <v>2.625341244100166</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.05700510479573341</v>
+        <v>0.05619074615579436</v>
       </c>
       <c r="W71">
-        <v>0.2223581962891661</v>
+        <v>0.2225502220564637</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2375212699822227</v>
+        <v>0.2341281089824765</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2078307029075586</v>
+        <v>0.2097307029075586</v>
       </c>
       <c r="C72">
-        <v>-1142.79431852491</v>
+        <v>-1180.618934139415</v>
       </c>
       <c r="D72">
-        <v>823.6756814750902</v>
+        <v>814.9620658605855</v>
       </c>
       <c r="E72">
-        <v>1140.87</v>
+        <v>1169.981</v>
       </c>
       <c r="F72">
-        <v>2037.77</v>
+        <v>2066.881</v>
       </c>
       <c r="G72">
         <v>71.3</v>
@@ -7197,37 +7197,37 @@
         <v>112.5</v>
       </c>
       <c r="M72">
-        <v>480.5061660000001</v>
+        <v>487.3705398000001</v>
       </c>
       <c r="N72">
-        <v>-368.0061660000001</v>
+        <v>-374.8705398000001</v>
       </c>
       <c r="O72">
-        <v>-88.32147984000002</v>
+        <v>-89.96892955200002</v>
       </c>
       <c r="P72">
-        <v>-279.6846861600001</v>
+        <v>-284.9016102480001</v>
       </c>
       <c r="Q72">
-        <v>-57.78468616000006</v>
+        <v>-63.00161024800005</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1734851582267801</v>
+        <v>0.1778880947173588</v>
       </c>
       <c r="T72">
-        <v>2.625341244100166</v>
+        <v>2.715870252517413</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.05619074615579436</v>
+        <v>0.0553993271958536</v>
       </c>
       <c r="W72">
-        <v>0.2225502220564637</v>
+        <v>0.2227368386472177</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2341281089824765</v>
+        <v>0.2308305299827234</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2097307029075586</v>
+        <v>0.2116307029075586</v>
       </c>
       <c r="C73">
-        <v>-1180.618934139414</v>
+        <v>-1218.261118054369</v>
       </c>
       <c r="D73">
-        <v>814.9620658605859</v>
+        <v>806.4308819456306</v>
       </c>
       <c r="E73">
-        <v>1169.981</v>
+        <v>1199.092</v>
       </c>
       <c r="F73">
-        <v>2066.881</v>
+        <v>2095.992</v>
       </c>
       <c r="G73">
         <v>71.3</v>
@@ -7279,37 +7279,37 @@
         <v>112.5</v>
       </c>
       <c r="M73">
-        <v>487.3705398</v>
+        <v>494.2349136</v>
       </c>
       <c r="N73">
-        <v>-374.8705398</v>
+        <v>-381.7349136</v>
       </c>
       <c r="O73">
-        <v>-89.96892955199999</v>
+        <v>-91.616379264</v>
       </c>
       <c r="P73">
-        <v>-284.901610248</v>
+        <v>-290.118534336</v>
       </c>
       <c r="Q73">
-        <v>-63.00161024799999</v>
+        <v>-68.21853433600003</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1778880947173587</v>
+        <v>0.1826055266715501</v>
       </c>
       <c r="T73">
-        <v>2.715870252517412</v>
+        <v>2.812865618678748</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.05539932719585361</v>
+        <v>0.0546298920959112</v>
       </c>
       <c r="W73">
-        <v>0.2227368386472177</v>
+        <v>0.2229182714437841</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2308305299827235</v>
+        <v>0.2276245503996299</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2116307029075586</v>
+        <v>0.2135307029075586</v>
       </c>
       <c r="C74">
-        <v>-1218.261118054369</v>
+        <v>-1255.726540109988</v>
       </c>
       <c r="D74">
-        <v>806.4308819456306</v>
+        <v>798.0764598900121</v>
       </c>
       <c r="E74">
-        <v>1199.092</v>
+        <v>1228.203</v>
       </c>
       <c r="F74">
-        <v>2095.992</v>
+        <v>2125.103</v>
       </c>
       <c r="G74">
         <v>71.3</v>
@@ -7361,37 +7361,37 @@
         <v>112.5</v>
       </c>
       <c r="M74">
-        <v>494.2349136</v>
+        <v>501.0992874</v>
       </c>
       <c r="N74">
-        <v>-381.7349136</v>
+        <v>-388.5992874000001</v>
       </c>
       <c r="O74">
-        <v>-91.616379264</v>
+        <v>-93.26382897600001</v>
       </c>
       <c r="P74">
-        <v>-290.118534336</v>
+        <v>-295.3354584240001</v>
       </c>
       <c r="Q74">
-        <v>-68.21853433600003</v>
+        <v>-73.43545842400007</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1826055266715501</v>
+        <v>0.1876723980297556</v>
       </c>
       <c r="T74">
-        <v>2.812865618678748</v>
+        <v>2.917045826777961</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.0546298920959112</v>
+        <v>0.05388153740966584</v>
       </c>
       <c r="W74">
-        <v>0.2229182714437841</v>
+        <v>0.2230947334788008</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2276245503996299</v>
+        <v>0.2245064058736076</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2135307029075586</v>
+        <v>0.2154307029075586</v>
       </c>
       <c r="C75">
-        <v>-1255.726540109988</v>
+        <v>-1293.020637603073</v>
       </c>
       <c r="D75">
-        <v>798.0764598900121</v>
+        <v>789.893362396927</v>
       </c>
       <c r="E75">
-        <v>1228.203</v>
+        <v>1257.314</v>
       </c>
       <c r="F75">
-        <v>2125.103</v>
+        <v>2154.214</v>
       </c>
       <c r="G75">
         <v>71.3</v>
@@ -7443,37 +7443,37 @@
         <v>112.5</v>
       </c>
       <c r="M75">
-        <v>501.0992874</v>
+        <v>507.9636612</v>
       </c>
       <c r="N75">
-        <v>-388.5992874000001</v>
+        <v>-395.4636612</v>
       </c>
       <c r="O75">
-        <v>-93.26382897600001</v>
+        <v>-94.91127868800001</v>
       </c>
       <c r="P75">
-        <v>-295.3354584240001</v>
+        <v>-300.552382512</v>
       </c>
       <c r="Q75">
-        <v>-73.43545842400007</v>
+        <v>-78.652382512</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1876723980297556</v>
+        <v>0.1931290287232078</v>
       </c>
       <c r="T75">
-        <v>2.917045826777961</v>
+        <v>3.029239897038651</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.05388153740966584</v>
+        <v>0.05315340852575143</v>
       </c>
       <c r="W75">
-        <v>0.2230947334788008</v>
+        <v>0.2232664262696278</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2245064058736076</v>
+        <v>0.2214725355239643</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2154307029075586</v>
+        <v>0.2173307029075586</v>
       </c>
       <c r="C76">
-        <v>-1293.020637603073</v>
+        <v>-1330.148627087966</v>
       </c>
       <c r="D76">
-        <v>789.893362396927</v>
+        <v>781.8763729120341</v>
       </c>
       <c r="E76">
-        <v>1257.314</v>
+        <v>1286.425</v>
       </c>
       <c r="F76">
-        <v>2154.214</v>
+        <v>2183.325</v>
       </c>
       <c r="G76">
         <v>71.3</v>
@@ -7525,37 +7525,37 @@
         <v>112.5</v>
       </c>
       <c r="M76">
-        <v>507.9636612</v>
+        <v>514.828035</v>
       </c>
       <c r="N76">
-        <v>-395.4636612</v>
+        <v>-402.328035</v>
       </c>
       <c r="O76">
-        <v>-94.91127868800001</v>
+        <v>-96.55872839999999</v>
       </c>
       <c r="P76">
-        <v>-300.552382512</v>
+        <v>-305.7693066</v>
       </c>
       <c r="Q76">
-        <v>-78.652382512</v>
+        <v>-83.86930659999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1931290287232078</v>
+        <v>0.1990221898721361</v>
       </c>
       <c r="T76">
-        <v>3.029239897038651</v>
+        <v>3.150409492920198</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.05315340852575143</v>
+        <v>0.05244469641207475</v>
       </c>
       <c r="W76">
-        <v>0.2232664262696278</v>
+        <v>0.2234335405860328</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2214725355239643</v>
+        <v>0.2185195683836448</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2173307029075586</v>
+        <v>0.2192307029075586</v>
       </c>
       <c r="C77">
-        <v>-1330.148627087966</v>
+        <v>-1367.115515466076</v>
       </c>
       <c r="D77">
-        <v>781.8763729120341</v>
+        <v>774.0204845339238</v>
       </c>
       <c r="E77">
-        <v>1286.425</v>
+        <v>1315.536</v>
       </c>
       <c r="F77">
-        <v>2183.325</v>
+        <v>2212.436</v>
       </c>
       <c r="G77">
         <v>71.3</v>
@@ -7607,37 +7607,37 @@
         <v>112.5</v>
       </c>
       <c r="M77">
-        <v>514.828035</v>
+        <v>521.6924088000001</v>
       </c>
       <c r="N77">
-        <v>-402.328035</v>
+        <v>-409.1924088000001</v>
       </c>
       <c r="O77">
-        <v>-96.55872839999999</v>
+        <v>-98.20617811200002</v>
       </c>
       <c r="P77">
-        <v>-305.7693066</v>
+        <v>-310.986230688</v>
       </c>
       <c r="Q77">
-        <v>-83.86930659999999</v>
+        <v>-89.08623068800003</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1990221898721361</v>
+        <v>0.2054064477834751</v>
       </c>
       <c r="T77">
-        <v>3.150409492920198</v>
+        <v>3.281676555125206</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.05244469641207475</v>
+        <v>0.05175463461717902</v>
       </c>
       <c r="W77">
-        <v>0.2234335405860328</v>
+        <v>0.2235962571572692</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2185195683836448</v>
+        <v>0.2156443109049127</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2192307029075586</v>
+        <v>0.2211307029075586</v>
       </c>
       <c r="C78">
-        <v>-1367.115515466076</v>
+        <v>-1403.926110413528</v>
       </c>
       <c r="D78">
-        <v>774.0204845339238</v>
+        <v>766.3208895864723</v>
       </c>
       <c r="E78">
-        <v>1315.536</v>
+        <v>1344.647</v>
       </c>
       <c r="F78">
-        <v>2212.436</v>
+        <v>2241.547</v>
       </c>
       <c r="G78">
         <v>71.3</v>
@@ -7689,37 +7689,37 @@
         <v>112.5</v>
       </c>
       <c r="M78">
-        <v>521.6924088000001</v>
+        <v>528.5567826</v>
       </c>
       <c r="N78">
-        <v>-409.1924088000001</v>
+        <v>-416.0567826</v>
       </c>
       <c r="O78">
-        <v>-98.20617811200002</v>
+        <v>-99.853627824</v>
       </c>
       <c r="P78">
-        <v>-310.986230688</v>
+        <v>-316.203154776</v>
       </c>
       <c r="Q78">
-        <v>-89.08623068800003</v>
+        <v>-94.30315477600001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2054064477834751</v>
+        <v>0.2123458585566697</v>
       </c>
       <c r="T78">
-        <v>3.281676555125206</v>
+        <v>3.424358144478477</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.05175463461717902</v>
+        <v>0.05108249650526761</v>
       </c>
       <c r="W78">
-        <v>0.2235962571572692</v>
+        <v>0.2237547473240579</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2156443109049127</v>
+        <v>0.2128437354386151</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2211307029075586</v>
+        <v>0.2230307029075586</v>
       </c>
       <c r="C79">
-        <v>-1403.926110413528</v>
+        <v>-1440.585030192563</v>
       </c>
       <c r="D79">
-        <v>766.3208895864723</v>
+        <v>758.7729698074368</v>
       </c>
       <c r="E79">
-        <v>1344.647</v>
+        <v>1373.758</v>
       </c>
       <c r="F79">
-        <v>2241.547</v>
+        <v>2270.658</v>
       </c>
       <c r="G79">
         <v>71.3</v>
@@ -7771,37 +7771,37 @@
         <v>112.5</v>
       </c>
       <c r="M79">
-        <v>528.5567826</v>
+        <v>535.4211564</v>
       </c>
       <c r="N79">
-        <v>-416.0567826</v>
+        <v>-422.9211564</v>
       </c>
       <c r="O79">
-        <v>-99.853627824</v>
+        <v>-101.501077536</v>
       </c>
       <c r="P79">
-        <v>-316.203154776</v>
+        <v>-321.420078864</v>
       </c>
       <c r="Q79">
-        <v>-94.30315477600001</v>
+        <v>-99.520078864</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2123458585566697</v>
+        <v>0.2199161248547001</v>
       </c>
       <c r="T79">
-        <v>3.424358144478477</v>
+        <v>3.580010787409316</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.05108249650526761</v>
+        <v>0.05042759270391803</v>
       </c>
       <c r="W79">
-        <v>0.2237547473240579</v>
+        <v>0.2239091736404161</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2128437354386151</v>
+        <v>0.2101149695996585</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2230307029075586</v>
+        <v>0.2249307029075586</v>
       </c>
       <c r="C80">
-        <v>-1440.585030192563</v>
+        <v>-1477.096712888772</v>
       </c>
       <c r="D80">
-        <v>758.7729698074368</v>
+        <v>751.372287111228</v>
       </c>
       <c r="E80">
-        <v>1373.758</v>
+        <v>1402.869</v>
       </c>
       <c r="F80">
-        <v>2270.658</v>
+        <v>2299.769</v>
       </c>
       <c r="G80">
         <v>71.3</v>
@@ -7853,37 +7853,37 @@
         <v>112.5</v>
       </c>
       <c r="M80">
-        <v>535.4211564</v>
+        <v>542.2855302</v>
       </c>
       <c r="N80">
-        <v>-422.9211564</v>
+        <v>-429.7855302</v>
       </c>
       <c r="O80">
-        <v>-101.501077536</v>
+        <v>-103.148527248</v>
       </c>
       <c r="P80">
-        <v>-321.420078864</v>
+        <v>-326.637002952</v>
       </c>
       <c r="Q80">
-        <v>-99.520078864</v>
+        <v>-104.737002952</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2199161248547001</v>
+        <v>0.2282073688954001</v>
       </c>
       <c r="T80">
-        <v>3.580010787409316</v>
+        <v>3.750487491571665</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.05042759270391803</v>
+        <v>0.04978926874564058</v>
       </c>
       <c r="W80">
-        <v>0.2239091736404161</v>
+        <v>0.2240596904297779</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2101149695996585</v>
+        <v>0.2074552864401691</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2249307029075586</v>
+        <v>0.2268307029075586</v>
       </c>
       <c r="C81">
-        <v>-1477.096712888772</v>
+        <v>-1513.465425112971</v>
       </c>
       <c r="D81">
-        <v>751.372287111228</v>
+        <v>744.1145748870292</v>
       </c>
       <c r="E81">
-        <v>1402.869</v>
+        <v>1431.98</v>
       </c>
       <c r="F81">
-        <v>2299.769</v>
+        <v>2328.88</v>
       </c>
       <c r="G81">
         <v>71.3</v>
@@ -7935,37 +7935,37 @@
         <v>112.5</v>
       </c>
       <c r="M81">
-        <v>542.2855302</v>
+        <v>549.149904</v>
       </c>
       <c r="N81">
-        <v>-429.7855302</v>
+        <v>-436.649904</v>
       </c>
       <c r="O81">
-        <v>-103.148527248</v>
+        <v>-104.79597696</v>
       </c>
       <c r="P81">
-        <v>-326.637002952</v>
+        <v>-331.85392704</v>
       </c>
       <c r="Q81">
-        <v>-104.737002952</v>
+        <v>-109.95392704</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2282073688954001</v>
+        <v>0.2373277373401701</v>
       </c>
       <c r="T81">
-        <v>3.750487491571665</v>
+        <v>3.938011866150248</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.04978926874564058</v>
+        <v>0.04916690288632007</v>
       </c>
       <c r="W81">
-        <v>0.2240596904297779</v>
+        <v>0.2242064442994057</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2074552864401691</v>
+        <v>0.204862095359667</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2268307029075586</v>
+        <v>0.2287307029075586</v>
       </c>
       <c r="C82">
-        <v>-1513.465425112971</v>
+        <v>-1549.695270203586</v>
       </c>
       <c r="D82">
-        <v>744.1145748870292</v>
+        <v>736.995729796414</v>
       </c>
       <c r="E82">
-        <v>1431.98</v>
+        <v>1461.091</v>
       </c>
       <c r="F82">
-        <v>2328.88</v>
+        <v>2357.991</v>
       </c>
       <c r="G82">
         <v>71.3</v>
@@ -8017,37 +8017,37 @@
         <v>112.5</v>
       </c>
       <c r="M82">
-        <v>549.149904</v>
+        <v>556.0142778000001</v>
       </c>
       <c r="N82">
-        <v>-436.649904</v>
+        <v>-443.5142778000001</v>
       </c>
       <c r="O82">
-        <v>-104.79597696</v>
+        <v>-106.443426672</v>
       </c>
       <c r="P82">
-        <v>-331.85392704</v>
+        <v>-337.0708511280001</v>
       </c>
       <c r="Q82">
-        <v>-109.95392704</v>
+        <v>-115.1708511280001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2373277373401701</v>
+        <v>0.2474081445686002</v>
       </c>
       <c r="T82">
-        <v>3.938011866150248</v>
+        <v>4.145275648579209</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.04916690288632007</v>
+        <v>0.04855990408525439</v>
       </c>
       <c r="W82">
-        <v>0.2242064442994057</v>
+        <v>0.224349574616697</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.204862095359667</v>
+        <v>0.20233293368856</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2287307029075586</v>
+        <v>0.2306307029075586</v>
       </c>
       <c r="C83">
-        <v>-1549.695270203586</v>
+        <v>-1585.790195962669</v>
       </c>
       <c r="D83">
-        <v>736.995729796414</v>
+        <v>730.0118040373317</v>
       </c>
       <c r="E83">
-        <v>1461.091</v>
+        <v>1490.202</v>
       </c>
       <c r="F83">
-        <v>2357.991</v>
+        <v>2387.102</v>
       </c>
       <c r="G83">
         <v>71.3</v>
@@ -8099,37 +8099,37 @@
         <v>112.5</v>
       </c>
       <c r="M83">
-        <v>556.0142778000001</v>
+        <v>562.8786516000001</v>
       </c>
       <c r="N83">
-        <v>-443.5142778000001</v>
+        <v>-450.3786516000001</v>
       </c>
       <c r="O83">
-        <v>-106.443426672</v>
+        <v>-108.090876384</v>
       </c>
       <c r="P83">
-        <v>-337.0708511280001</v>
+        <v>-342.2877752160001</v>
       </c>
       <c r="Q83">
-        <v>-115.1708511280001</v>
+        <v>-120.3877752160001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2474081445686002</v>
+        <v>0.2586085970446335</v>
       </c>
       <c r="T83">
-        <v>4.145275648579209</v>
+        <v>4.375568740166943</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04855990408525439</v>
+        <v>0.04796771013299519</v>
       </c>
       <c r="W83">
-        <v>0.224349574616697</v>
+        <v>0.2244892139506398</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.20233293368856</v>
+        <v>0.19986545888748</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2306307029075586</v>
+        <v>0.2325307029075586</v>
       </c>
       <c r="C84">
-        <v>-1585.790195962669</v>
+        <v>-1621.754001956192</v>
       </c>
       <c r="D84">
-        <v>730.0118040373317</v>
+        <v>723.1589980438081</v>
       </c>
       <c r="E84">
-        <v>1490.202</v>
+        <v>1519.313</v>
       </c>
       <c r="F84">
-        <v>2387.102</v>
+        <v>2416.213</v>
       </c>
       <c r="G84">
         <v>71.3</v>
@@ -8181,37 +8181,37 @@
         <v>112.5</v>
       </c>
       <c r="M84">
-        <v>562.8786516000001</v>
+        <v>569.7430254000001</v>
       </c>
       <c r="N84">
-        <v>-450.3786516000001</v>
+        <v>-457.2430254000001</v>
       </c>
       <c r="O84">
-        <v>-108.090876384</v>
+        <v>-109.738326096</v>
       </c>
       <c r="P84">
-        <v>-342.2877752160001</v>
+        <v>-347.504699304</v>
       </c>
       <c r="Q84">
-        <v>-120.3877752160001</v>
+        <v>-125.604699304</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2586085970446335</v>
+        <v>0.2711267498119649</v>
       </c>
       <c r="T84">
-        <v>4.375568740166943</v>
+        <v>4.632955136647351</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04796771013299519</v>
+        <v>0.04738978591452537</v>
       </c>
       <c r="W84">
-        <v>0.2244892139506398</v>
+        <v>0.2246254884813549</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.19986545888748</v>
+        <v>0.1974574413105225</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2325307029075586</v>
+        <v>0.2344307029075586</v>
       </c>
       <c r="C85">
-        <v>-1621.754001956192</v>
+        <v>-1657.590346406997</v>
       </c>
       <c r="D85">
-        <v>723.1589980438081</v>
+        <v>716.4336535930034</v>
       </c>
       <c r="E85">
-        <v>1519.313</v>
+        <v>1548.424</v>
       </c>
       <c r="F85">
-        <v>2416.213</v>
+        <v>2445.324</v>
       </c>
       <c r="G85">
         <v>71.3</v>
@@ -8263,37 +8263,37 @@
         <v>112.5</v>
       </c>
       <c r="M85">
-        <v>569.7430254000001</v>
+        <v>576.6073992</v>
       </c>
       <c r="N85">
-        <v>-457.2430254000001</v>
+        <v>-464.1073992</v>
       </c>
       <c r="O85">
-        <v>-109.738326096</v>
+        <v>-111.385775808</v>
       </c>
       <c r="P85">
-        <v>-347.504699304</v>
+        <v>-352.721623392</v>
       </c>
       <c r="Q85">
-        <v>-125.604699304</v>
+        <v>-130.821623392</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2711267498119649</v>
+        <v>0.2852096716752127</v>
       </c>
       <c r="T85">
-        <v>4.632955136647351</v>
+        <v>4.922514832687812</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04738978591452537</v>
+        <v>0.04682562179649531</v>
       </c>
       <c r="W85">
-        <v>0.2246254884813549</v>
+        <v>0.2247585183803864</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1974574413105225</v>
+        <v>0.1951067574853972</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2344307029075586</v>
+        <v>0.2363307029075586</v>
       </c>
       <c r="C86">
-        <v>-1657.590346406996</v>
+        <v>-1693.302752706649</v>
       </c>
       <c r="D86">
-        <v>716.4336535930034</v>
+        <v>709.8322472933514</v>
       </c>
       <c r="E86">
-        <v>1548.424</v>
+        <v>1577.535</v>
       </c>
       <c r="F86">
-        <v>2445.324</v>
+        <v>2474.435</v>
       </c>
       <c r="G86">
         <v>71.3</v>
@@ -8345,37 +8345,37 @@
         <v>112.5</v>
       </c>
       <c r="M86">
-        <v>576.6073991999999</v>
+        <v>583.471773</v>
       </c>
       <c r="N86">
-        <v>-464.1073991999999</v>
+        <v>-470.971773</v>
       </c>
       <c r="O86">
-        <v>-111.385775808</v>
+        <v>-113.03322552</v>
       </c>
       <c r="P86">
-        <v>-352.721623392</v>
+        <v>-357.93854748</v>
       </c>
       <c r="Q86">
-        <v>-130.821623392</v>
+        <v>-136.03854748</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2852096716752126</v>
+        <v>0.3011703164535601</v>
       </c>
       <c r="T86">
-        <v>4.922514832687809</v>
+        <v>5.250682488200329</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04682562179649532</v>
+        <v>0.04627473212830125</v>
       </c>
       <c r="W86">
-        <v>0.2247585183803864</v>
+        <v>0.2248884181641466</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1951067574853972</v>
+        <v>0.192811383867922</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2363307029075586</v>
+        <v>0.2382307029075586</v>
       </c>
       <c r="C87">
-        <v>-1693.302752706649</v>
+        <v>-1728.89461557058</v>
       </c>
       <c r="D87">
-        <v>709.8322472933514</v>
+        <v>703.3513844294202</v>
       </c>
       <c r="E87">
-        <v>1577.535</v>
+        <v>1606.646</v>
       </c>
       <c r="F87">
-        <v>2474.435</v>
+        <v>2503.546</v>
       </c>
       <c r="G87">
         <v>71.3</v>
@@ -8427,37 +8427,37 @@
         <v>112.5</v>
       </c>
       <c r="M87">
-        <v>583.471773</v>
+        <v>590.3361467999999</v>
       </c>
       <c r="N87">
-        <v>-470.971773</v>
+        <v>-477.8361467999999</v>
       </c>
       <c r="O87">
-        <v>-113.03322552</v>
+        <v>-114.680675232</v>
       </c>
       <c r="P87">
-        <v>-357.93854748</v>
+        <v>-363.1554715679999</v>
       </c>
       <c r="Q87">
-        <v>-136.03854748</v>
+        <v>-141.2554715679999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3011703164535601</v>
+        <v>0.3194110533431001</v>
       </c>
       <c r="T87">
-        <v>5.250682488200329</v>
+        <v>5.625731237357495</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04627473212830125</v>
+        <v>0.04573665384773961</v>
       </c>
       <c r="W87">
-        <v>0.2248884181641466</v>
+        <v>0.225015297022703</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.192811383867922</v>
+        <v>0.1905693910322485</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2382307029075586</v>
+        <v>0.2401307029075586</v>
       </c>
       <c r="C88">
-        <v>-1728.89461557058</v>
+        <v>-1764.369206859091</v>
       </c>
       <c r="D88">
-        <v>703.3513844294202</v>
+        <v>696.9877931409092</v>
       </c>
       <c r="E88">
-        <v>1606.646</v>
+        <v>1635.757</v>
       </c>
       <c r="F88">
-        <v>2503.546</v>
+        <v>2532.657</v>
       </c>
       <c r="G88">
         <v>71.3</v>
@@ -8509,37 +8509,37 @@
         <v>112.5</v>
       </c>
       <c r="M88">
-        <v>590.3361467999999</v>
+        <v>597.2005206</v>
       </c>
       <c r="N88">
-        <v>-477.8361467999999</v>
+        <v>-484.7005206</v>
       </c>
       <c r="O88">
-        <v>-114.680675232</v>
+        <v>-116.328124944</v>
       </c>
       <c r="P88">
-        <v>-363.1554715679999</v>
+        <v>-368.372395656</v>
       </c>
       <c r="Q88">
-        <v>-141.2554715679999</v>
+        <v>-146.472395656</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3194110533431001</v>
+        <v>0.3404580574464155</v>
       </c>
       <c r="T88">
-        <v>5.625731237357495</v>
+        <v>6.058479794077303</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04573665384773961</v>
+        <v>0.04521094518282306</v>
       </c>
       <c r="W88">
-        <v>0.225015297022703</v>
+        <v>0.2251392591258903</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1905693910322485</v>
+        <v>0.1883789382617628</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2401307029075586</v>
+        <v>0.2420307029075586</v>
       </c>
       <c r="C89">
-        <v>-1764.369206859091</v>
+        <v>-1799.729681085196</v>
       </c>
       <c r="D89">
-        <v>696.9877931409092</v>
+        <v>690.7383189148042</v>
       </c>
       <c r="E89">
-        <v>1635.757</v>
+        <v>1664.868</v>
       </c>
       <c r="F89">
-        <v>2532.657</v>
+        <v>2561.768</v>
       </c>
       <c r="G89">
         <v>71.3</v>
@@ -8591,37 +8591,37 @@
         <v>112.5</v>
       </c>
       <c r="M89">
-        <v>597.2005206</v>
+        <v>604.0648944000001</v>
       </c>
       <c r="N89">
-        <v>-484.7005206</v>
+        <v>-491.5648944000001</v>
       </c>
       <c r="O89">
-        <v>-116.328124944</v>
+        <v>-117.975574656</v>
       </c>
       <c r="P89">
-        <v>-368.372395656</v>
+        <v>-373.5893197440001</v>
       </c>
       <c r="Q89">
-        <v>-146.472395656</v>
+        <v>-151.6893197440001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3404580574464155</v>
+        <v>0.3650128955669502</v>
       </c>
       <c r="T89">
-        <v>6.058479794077303</v>
+        <v>6.563353110250413</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04521094518282306</v>
+        <v>0.04469718444210915</v>
       </c>
       <c r="W89">
-        <v>0.2251392591258903</v>
+        <v>0.2252604039085507</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1883789382617628</v>
+        <v>0.1862382685087882</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2420307029075586</v>
+        <v>0.2439307029075586</v>
       </c>
       <c r="C90">
-        <v>-1799.729681085196</v>
+        <v>-1834.979080628786</v>
       </c>
       <c r="D90">
-        <v>690.7383189148042</v>
+        <v>684.5999193712139</v>
       </c>
       <c r="E90">
-        <v>1664.868</v>
+        <v>1693.979</v>
       </c>
       <c r="F90">
-        <v>2561.768</v>
+        <v>2590.879</v>
       </c>
       <c r="G90">
         <v>71.3</v>
@@ -8673,37 +8673,37 @@
         <v>112.5</v>
       </c>
       <c r="M90">
-        <v>604.0648944000001</v>
+        <v>610.9292682</v>
       </c>
       <c r="N90">
-        <v>-491.5648944000001</v>
+        <v>-498.4292682</v>
       </c>
       <c r="O90">
-        <v>-117.975574656</v>
+        <v>-119.623024368</v>
       </c>
       <c r="P90">
-        <v>-373.5893197440001</v>
+        <v>-378.806243832</v>
       </c>
       <c r="Q90">
-        <v>-151.6893197440001</v>
+        <v>-156.906243832</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3650128955669502</v>
+        <v>0.3940322497094002</v>
       </c>
       <c r="T90">
-        <v>6.563353110250413</v>
+        <v>7.160021574818632</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04469718444210915</v>
+        <v>0.04419496888657984</v>
       </c>
       <c r="W90">
-        <v>0.2252604039085507</v>
+        <v>0.2253788263365445</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1862382685087882</v>
+        <v>0.1841457036940827</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2439307029075586</v>
+        <v>0.2458307029075586</v>
       </c>
       <c r="C91">
-        <v>-1834.979080628786</v>
+        <v>-1870.12034067522</v>
       </c>
       <c r="D91">
-        <v>684.5999193712139</v>
+        <v>678.5696593247795</v>
       </c>
       <c r="E91">
-        <v>1693.979</v>
+        <v>1723.09</v>
       </c>
       <c r="F91">
-        <v>2590.879</v>
+        <v>2619.99</v>
       </c>
       <c r="G91">
         <v>71.3</v>
@@ -8755,37 +8755,37 @@
         <v>112.5</v>
       </c>
       <c r="M91">
-        <v>610.9292682</v>
+        <v>617.793642</v>
       </c>
       <c r="N91">
-        <v>-498.4292682</v>
+        <v>-505.293642</v>
       </c>
       <c r="O91">
-        <v>-119.623024368</v>
+        <v>-121.27047408</v>
       </c>
       <c r="P91">
-        <v>-378.806243832</v>
+        <v>-384.02316792</v>
       </c>
       <c r="Q91">
-        <v>-156.906243832</v>
+        <v>-162.12316792</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3940322497094002</v>
+        <v>0.4288554746803402</v>
       </c>
       <c r="T91">
-        <v>7.160021574818632</v>
+        <v>7.876023732300496</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04419496888657984</v>
+        <v>0.04370391367672895</v>
       </c>
       <c r="W91">
-        <v>0.2253788263365445</v>
+        <v>0.2254946171550273</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1841457036940827</v>
+        <v>0.182099640319704</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2458307029075586</v>
+        <v>0.2477307029075586</v>
       </c>
       <c r="C92">
-        <v>-1870.12034067522</v>
+        <v>-1905.156293895191</v>
       </c>
       <c r="D92">
-        <v>678.5696593247795</v>
+        <v>672.6447061048096</v>
       </c>
       <c r="E92">
-        <v>1723.09</v>
+        <v>1752.201</v>
       </c>
       <c r="F92">
-        <v>2619.99</v>
+        <v>2649.101</v>
       </c>
       <c r="G92">
         <v>71.3</v>
@@ -8837,37 +8837,37 @@
         <v>112.5</v>
       </c>
       <c r="M92">
-        <v>617.793642</v>
+        <v>624.6580158</v>
       </c>
       <c r="N92">
-        <v>-505.293642</v>
+        <v>-512.1580158</v>
       </c>
       <c r="O92">
-        <v>-121.27047408</v>
+        <v>-122.917923792</v>
       </c>
       <c r="P92">
-        <v>-384.02316792</v>
+        <v>-389.240092008</v>
       </c>
       <c r="Q92">
-        <v>-162.12316792</v>
+        <v>-167.340092008</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4288554746803402</v>
+        <v>0.471417194089267</v>
       </c>
       <c r="T92">
-        <v>7.876023732300496</v>
+        <v>8.751137480333886</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04370391367672895</v>
+        <v>0.04322365088907259</v>
       </c>
       <c r="W92">
-        <v>0.2254946171550273</v>
+        <v>0.2256078631203567</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.182099640319704</v>
+        <v>0.1800985453711359</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2477307029075586</v>
+        <v>0.2496307029075586</v>
       </c>
       <c r="C93">
-        <v>-1905.156293895191</v>
+        <v>-1940.089674881528</v>
       </c>
       <c r="D93">
-        <v>672.6447061048096</v>
+        <v>666.8223251184716</v>
       </c>
       <c r="E93">
-        <v>1752.201</v>
+        <v>1781.312</v>
       </c>
       <c r="F93">
-        <v>2649.101</v>
+        <v>2678.212</v>
       </c>
       <c r="G93">
         <v>71.3</v>
@@ -8919,37 +8919,37 @@
         <v>112.5</v>
       </c>
       <c r="M93">
-        <v>624.6580158</v>
+        <v>631.5223896</v>
       </c>
       <c r="N93">
-        <v>-512.1580158</v>
+        <v>-519.0223896</v>
       </c>
       <c r="O93">
-        <v>-122.917923792</v>
+        <v>-124.565373504</v>
       </c>
       <c r="P93">
-        <v>-389.240092008</v>
+        <v>-394.457016096</v>
       </c>
       <c r="Q93">
-        <v>-167.340092008</v>
+        <v>-172.557016096</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.471417194089267</v>
+        <v>0.5246193433504255</v>
       </c>
       <c r="T93">
-        <v>8.751137480333886</v>
+        <v>9.845029665375623</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.04322365088907259</v>
+        <v>0.04275382859680007</v>
       </c>
       <c r="W93">
-        <v>0.2256078631203567</v>
+        <v>0.2257186472168745</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1800985453711359</v>
+        <v>0.1781409524866669</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2496307029075586</v>
+        <v>0.2515307029075586</v>
       </c>
       <c r="C94">
-        <v>-1940.089674881528</v>
+        <v>-1974.923124357569</v>
       </c>
       <c r="D94">
-        <v>666.8223251184716</v>
+        <v>661.0998756424309</v>
       </c>
       <c r="E94">
-        <v>1781.312</v>
+        <v>1810.423</v>
       </c>
       <c r="F94">
-        <v>2678.212</v>
+        <v>2707.323</v>
       </c>
       <c r="G94">
         <v>71.3</v>
@@ -9001,37 +9001,37 @@
         <v>112.5</v>
       </c>
       <c r="M94">
-        <v>631.5223896</v>
+        <v>638.3867633999999</v>
       </c>
       <c r="N94">
-        <v>-519.0223896</v>
+        <v>-525.8867633999999</v>
       </c>
       <c r="O94">
-        <v>-124.565373504</v>
+        <v>-126.212823216</v>
       </c>
       <c r="P94">
-        <v>-394.457016096</v>
+        <v>-399.6739401839999</v>
       </c>
       <c r="Q94">
-        <v>-172.557016096</v>
+        <v>-177.7739401839999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5246193433504255</v>
+        <v>0.5930221066862006</v>
       </c>
       <c r="T94">
-        <v>9.845029665375623</v>
+        <v>11.251462474715</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04275382859680007</v>
+        <v>0.0422941100097377</v>
       </c>
       <c r="W94">
-        <v>0.2257186472168745</v>
+        <v>0.2258270488597039</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1781409524866669</v>
+        <v>0.1762254583739071</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2515307029075586</v>
+        <v>0.2534307029075586</v>
       </c>
       <c r="C95">
-        <v>-1974.923124357569</v>
+        <v>-2009.659193170663</v>
       </c>
       <c r="D95">
-        <v>661.0998756424309</v>
+        <v>655.4748068293374</v>
       </c>
       <c r="E95">
-        <v>1810.423</v>
+        <v>1839.534</v>
       </c>
       <c r="F95">
-        <v>2707.323</v>
+        <v>2736.434</v>
       </c>
       <c r="G95">
         <v>71.3</v>
@@ -9083,37 +9083,37 @@
         <v>112.5</v>
       </c>
       <c r="M95">
-        <v>638.3867633999999</v>
+        <v>645.2511372</v>
       </c>
       <c r="N95">
-        <v>-525.8867633999999</v>
+        <v>-532.7511372</v>
       </c>
       <c r="O95">
-        <v>-126.212823216</v>
+        <v>-127.860272928</v>
       </c>
       <c r="P95">
-        <v>-399.6739401839999</v>
+        <v>-404.890864272</v>
       </c>
       <c r="Q95">
-        <v>-177.7739401839999</v>
+        <v>-182.990864272</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5930221066862006</v>
+        <v>0.6842257911339009</v>
       </c>
       <c r="T95">
-        <v>11.251462474715</v>
+        <v>13.12670622050084</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.0422941100097377</v>
+        <v>0.04184417266920857</v>
       </c>
       <c r="W95">
-        <v>0.2258270488597039</v>
+        <v>0.2259331440846006</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1762254583739071</v>
+        <v>0.1743507194550358</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2534307029075586</v>
+        <v>0.2553307029075587</v>
       </c>
       <c r="C96">
-        <v>-2009.659193170663</v>
+        <v>-2044.300346083533</v>
       </c>
       <c r="D96">
-        <v>655.4748068293374</v>
+        <v>649.9446539164669</v>
       </c>
       <c r="E96">
-        <v>1839.534</v>
+        <v>1868.645</v>
       </c>
       <c r="F96">
-        <v>2736.434</v>
+        <v>2765.545</v>
       </c>
       <c r="G96">
         <v>71.3</v>
@@ -9165,37 +9165,37 @@
         <v>112.5</v>
       </c>
       <c r="M96">
-        <v>645.2511372</v>
+        <v>652.1155110000001</v>
       </c>
       <c r="N96">
-        <v>-532.7511372</v>
+        <v>-539.6155110000001</v>
       </c>
       <c r="O96">
-        <v>-127.860272928</v>
+        <v>-129.50772264</v>
       </c>
       <c r="P96">
-        <v>-404.890864272</v>
+        <v>-410.1077883600001</v>
       </c>
       <c r="Q96">
-        <v>-182.990864272</v>
+        <v>-188.2077883600001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6842257911339009</v>
+        <v>0.8119109493606814</v>
       </c>
       <c r="T96">
-        <v>13.12670622050084</v>
+        <v>15.75204746460101</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04184417266920857</v>
+        <v>0.04140370769374321</v>
       </c>
       <c r="W96">
-        <v>0.2259331440846006</v>
+        <v>0.2260370057258154</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1743507194550358</v>
+        <v>0.1725154487239301</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2553307029075587</v>
+        <v>0.2572307029075586</v>
       </c>
       <c r="C97">
-        <v>-2044.300346083533</v>
+        <v>-2078.848965375319</v>
       </c>
       <c r="D97">
-        <v>649.9446539164669</v>
+        <v>644.5070346246805</v>
       </c>
       <c r="E97">
-        <v>1868.645</v>
+        <v>1897.756</v>
       </c>
       <c r="F97">
-        <v>2765.545</v>
+        <v>2794.656</v>
       </c>
       <c r="G97">
         <v>71.3</v>
@@ -9247,37 +9247,37 @@
         <v>112.5</v>
       </c>
       <c r="M97">
-        <v>652.1155110000001</v>
+        <v>658.9798848</v>
       </c>
       <c r="N97">
-        <v>-539.6155110000001</v>
+        <v>-546.4798848</v>
       </c>
       <c r="O97">
-        <v>-129.50772264</v>
+        <v>-131.155172352</v>
       </c>
       <c r="P97">
-        <v>-410.1077883600001</v>
+        <v>-415.324712448</v>
       </c>
       <c r="Q97">
-        <v>-188.2077883600001</v>
+        <v>-193.424712448</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8119109493606814</v>
+        <v>1.003438686700852</v>
       </c>
       <c r="T97">
-        <v>15.75204746460101</v>
+        <v>19.69005933075128</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04140370769374321</v>
+        <v>0.04097241907193339</v>
       </c>
       <c r="W97">
-        <v>0.2260370057258154</v>
+        <v>0.2261387035828381</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1725154487239301</v>
+        <v>0.1707184127997226</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2572307029075586</v>
+        <v>0.2591307029075586</v>
       </c>
       <c r="C98">
-        <v>-2078.848965375319</v>
+        <v>-2113.307354263351</v>
       </c>
       <c r="D98">
-        <v>644.5070346246808</v>
+        <v>639.1596457366484</v>
       </c>
       <c r="E98">
-        <v>1897.756</v>
+        <v>1926.867</v>
       </c>
       <c r="F98">
-        <v>2794.656</v>
+        <v>2823.767</v>
       </c>
       <c r="G98">
         <v>71.3</v>
@@ -9329,37 +9329,37 @@
         <v>112.5</v>
       </c>
       <c r="M98">
-        <v>658.9798848</v>
+        <v>665.8442586</v>
       </c>
       <c r="N98">
-        <v>-546.4798848</v>
+        <v>-553.3442586</v>
       </c>
       <c r="O98">
-        <v>-131.155172352</v>
+        <v>-132.802622064</v>
       </c>
       <c r="P98">
-        <v>-415.324712448</v>
+        <v>-420.541636536</v>
       </c>
       <c r="Q98">
-        <v>-193.424712448</v>
+        <v>-198.641636536</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.00343868670085</v>
+        <v>1.3226515822678</v>
       </c>
       <c r="T98">
-        <v>19.69005933075122</v>
+        <v>26.25341244100163</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04097241907193339</v>
+        <v>0.04055002299902687</v>
       </c>
       <c r="W98">
-        <v>0.2261387035828381</v>
+        <v>0.2262383045768295</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1707184127997226</v>
+        <v>0.1689584291626119</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2591307029075586</v>
+        <v>0.2610307029075586</v>
       </c>
       <c r="C99">
-        <v>-2113.307354263351</v>
+        <v>-2147.677740155989</v>
       </c>
       <c r="D99">
-        <v>639.1596457366484</v>
+        <v>633.900259844011</v>
       </c>
       <c r="E99">
-        <v>1926.867</v>
+        <v>1955.978</v>
       </c>
       <c r="F99">
-        <v>2823.767</v>
+        <v>2852.878</v>
       </c>
       <c r="G99">
         <v>71.3</v>
@@ -9411,37 +9411,37 @@
         <v>112.5</v>
       </c>
       <c r="M99">
-        <v>665.8442586</v>
+        <v>672.7086323999999</v>
       </c>
       <c r="N99">
-        <v>-553.3442586</v>
+        <v>-560.2086323999999</v>
       </c>
       <c r="O99">
-        <v>-132.802622064</v>
+        <v>-134.450071776</v>
       </c>
       <c r="P99">
-        <v>-420.541636536</v>
+        <v>-425.758560624</v>
       </c>
       <c r="Q99">
-        <v>-198.641636536</v>
+        <v>-203.858560624</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.3226515822678</v>
+        <v>1.961077373401699</v>
       </c>
       <c r="T99">
-        <v>26.25341244100163</v>
+        <v>39.38011866150244</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04055002299902687</v>
+        <v>0.04013624725413883</v>
       </c>
       <c r="W99">
-        <v>0.2262383045768295</v>
+        <v>0.2263358728974741</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1689584291626119</v>
+        <v>0.1672343635589119</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2610307029075586</v>
+        <v>0.2629307029075586</v>
       </c>
       <c r="C100">
-        <v>-2147.677740155989</v>
+        <v>-2181.962277746171</v>
       </c>
       <c r="D100">
-        <v>633.900259844011</v>
+        <v>628.7267222538286</v>
       </c>
       <c r="E100">
-        <v>1955.978</v>
+        <v>1985.089</v>
       </c>
       <c r="F100">
-        <v>2852.878</v>
+        <v>2881.989</v>
       </c>
       <c r="G100">
         <v>71.3</v>
@@ -9493,37 +9493,37 @@
         <v>112.5</v>
       </c>
       <c r="M100">
-        <v>672.7086323999999</v>
+        <v>679.5730062</v>
       </c>
       <c r="N100">
-        <v>-560.2086323999999</v>
+        <v>-567.0730062</v>
       </c>
       <c r="O100">
-        <v>-134.450071776</v>
+        <v>-136.097521488</v>
       </c>
       <c r="P100">
-        <v>-425.758560624</v>
+        <v>-430.975484712</v>
       </c>
       <c r="Q100">
-        <v>-203.858560624</v>
+        <v>-209.075484712</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.961077373401699</v>
+        <v>3.876354746803399</v>
       </c>
       <c r="T100">
-        <v>39.38011866150244</v>
+        <v>78.76023732300489</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04013624725413883</v>
+        <v>0.03973083061520814</v>
       </c>
       <c r="W100">
-        <v>0.2263358728974741</v>
+        <v>0.2264314701409339</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1672343635589119</v>
+        <v>0.1655451275633673</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2629307029075586</v>
-      </c>
-      <c r="C101">
-        <v>-2181.962277746171</v>
-      </c>
-      <c r="D101">
-        <v>628.7267222538286</v>
-      </c>
-      <c r="E101">
-        <v>1985.089</v>
-      </c>
-      <c r="F101">
-        <v>2881.989</v>
-      </c>
-      <c r="G101">
-        <v>71.3</v>
-      </c>
-      <c r="H101">
-        <v>2014.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>334.4</v>
-      </c>
-      <c r="K101">
-        <v>221.9</v>
-      </c>
-      <c r="L101">
-        <v>112.5</v>
-      </c>
-      <c r="M101">
-        <v>679.5730062</v>
-      </c>
-      <c r="N101">
-        <v>-567.0730062</v>
-      </c>
-      <c r="O101">
-        <v>-136.097521488</v>
-      </c>
-      <c r="P101">
-        <v>-430.975484712</v>
-      </c>
-      <c r="Q101">
-        <v>-209.075484712</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.876354746803399</v>
-      </c>
-      <c r="T101">
-        <v>78.76023732300489</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03973083061520814</v>
-      </c>
-      <c r="W101">
-        <v>0.2264314701409339</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1655451275633673</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
